--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135323935</v>
+        <v>135325593</v>
       </c>
       <c r="B2" t="n">
-        <v>96678</v>
+        <v>79992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2166</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619433</v>
+        <v>619420</v>
       </c>
       <c r="R2" t="n">
-        <v>7322100</v>
+        <v>7322107</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135325593</v>
+        <v>135325592</v>
       </c>
       <c r="B3" t="n">
-        <v>79992</v>
+        <v>79963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,10 +824,10 @@
         <v>619420</v>
       </c>
       <c r="R3" t="n">
-        <v>7322107</v>
+        <v>7322103</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,48 +897,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135323934</v>
+        <v>135323126</v>
       </c>
       <c r="B4" t="n">
-        <v>98066</v>
+        <v>92593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619430</v>
+        <v>619583</v>
       </c>
       <c r="R4" t="n">
-        <v>7322096</v>
+        <v>7322014</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,22 +992,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135325592</v>
+        <v>135323140</v>
       </c>
       <c r="B5" t="n">
-        <v>79963</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,37 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619420</v>
+        <v>619611</v>
       </c>
       <c r="R5" t="n">
-        <v>7322103</v>
+        <v>7322196</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,12 +1103,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1111,48 +1119,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135323126</v>
+        <v>135321345</v>
       </c>
       <c r="B6" t="n">
-        <v>92593</v>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619583</v>
+        <v>619545</v>
       </c>
       <c r="R6" t="n">
-        <v>7322014</v>
+        <v>7322019</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1222,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135323140</v>
+        <v>135322203</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>92245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,37 +1241,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619611</v>
+        <v>619565</v>
       </c>
       <c r="R7" t="n">
-        <v>7322196</v>
+        <v>7322022</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1333,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135321345</v>
+        <v>135323127</v>
       </c>
       <c r="B8" t="n">
         <v>92245</v>
@@ -1364,14 +1372,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619545</v>
+        <v>619583</v>
       </c>
       <c r="R8" t="n">
-        <v>7322019</v>
+        <v>7322014</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1403,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1413,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,12 +1436,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1444,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135322203</v>
+        <v>135323130</v>
       </c>
       <c r="B9" t="n">
         <v>92245</v>
@@ -1475,17 +1483,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619565</v>
+        <v>619604</v>
       </c>
       <c r="R9" t="n">
-        <v>7322022</v>
+        <v>7322053</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,12 +1547,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1555,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135323127</v>
+        <v>135323526</v>
       </c>
       <c r="B10" t="n">
         <v>92245</v>
@@ -1586,14 +1594,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619583</v>
+        <v>619613</v>
       </c>
       <c r="R10" t="n">
-        <v>7322014</v>
+        <v>7321994</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1625,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1635,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,23 +1658,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135323130</v>
+        <v>135323528</v>
       </c>
       <c r="B11" t="n">
         <v>92245</v>
@@ -1697,17 +1701,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619604</v>
+        <v>619630</v>
       </c>
       <c r="R11" t="n">
-        <v>7322053</v>
+        <v>7322002</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1746,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,27 +1761,43 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135323526</v>
+        <v>135326359</v>
       </c>
       <c r="B12" t="n">
         <v>92245</v>
@@ -1808,17 +1828,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619613</v>
+        <v>619563</v>
       </c>
       <c r="R12" t="n">
-        <v>7321994</v>
+        <v>7322050</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,19 +1892,23 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135323528</v>
+        <v>135330917</v>
       </c>
       <c r="B13" t="n">
         <v>92245</v>
@@ -1915,17 +1939,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619630</v>
+        <v>619675</v>
       </c>
       <c r="R13" t="n">
-        <v>7322002</v>
+        <v>7321985</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1954,7 +1978,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1964,7 +1988,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,46 +1999,30 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135326359</v>
+        <v>135325581</v>
       </c>
       <c r="B14" t="n">
-        <v>92245</v>
+        <v>79452</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,37 +2030,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619563</v>
+        <v>619648</v>
       </c>
       <c r="R14" t="n">
-        <v>7322050</v>
+        <v>7322061</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2081,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2091,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,12 +2114,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2122,45 +2130,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135330917</v>
+        <v>135325575</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92795</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619675</v>
+        <v>619645</v>
       </c>
       <c r="R15" t="n">
-        <v>7321985</v>
+        <v>7322036</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2202,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2233,45 +2241,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135325581</v>
+        <v>135329802</v>
       </c>
       <c r="B16" t="n">
-        <v>79452</v>
+        <v>92795</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619648</v>
+        <v>619620</v>
       </c>
       <c r="R16" t="n">
-        <v>7322061</v>
+        <v>7321986</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2303,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2321,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Granlåga nedbruten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,12 +2341,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2344,7 +2357,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135325575</v>
+        <v>135330939</v>
       </c>
       <c r="B17" t="n">
         <v>92795</v>
@@ -2375,17 +2388,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619645</v>
+        <v>619595</v>
       </c>
       <c r="R17" t="n">
-        <v>7322036</v>
+        <v>7322033</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2414,7 +2427,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2424,7 +2437,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,12 +2452,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2455,48 +2468,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135329802</v>
+        <v>135323123</v>
       </c>
       <c r="B18" t="n">
-        <v>92795</v>
+        <v>91970</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>918</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619620</v>
+        <v>619600</v>
       </c>
       <c r="R18" t="n">
-        <v>7321986</v>
+        <v>7322016</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2525,7 +2538,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2535,12 +2548,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Granlåga nedbruten</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,12 +2563,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2571,48 +2579,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135330939</v>
+        <v>135329816</v>
       </c>
       <c r="B19" t="n">
-        <v>92795</v>
+        <v>91970</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>918</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619595</v>
+        <v>619665</v>
       </c>
       <c r="R19" t="n">
-        <v>7322033</v>
+        <v>7321974</v>
       </c>
       <c r="S19" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,12 +2674,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2682,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135323123</v>
+        <v>135323527</v>
       </c>
       <c r="B20" t="n">
-        <v>91970</v>
+        <v>91974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,37 +2701,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619600</v>
+        <v>619616</v>
       </c>
       <c r="R20" t="n">
-        <v>7322016</v>
+        <v>7321993</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2752,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2777,26 +2785,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135329816</v>
+        <v>135325573</v>
       </c>
       <c r="B21" t="n">
-        <v>91970</v>
+        <v>91974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2804,34 +2808,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619665</v>
+        <v>619652</v>
       </c>
       <c r="R21" t="n">
-        <v>7321974</v>
+        <v>7322003</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2863,7 +2867,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2873,7 +2877,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,12 +2892,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2904,7 +2908,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135323527</v>
+        <v>135326358</v>
       </c>
       <c r="B22" t="n">
         <v>91974</v>
@@ -2935,17 +2939,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619616</v>
+        <v>619562</v>
       </c>
       <c r="R22" t="n">
-        <v>7321993</v>
+        <v>7322050</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2974,7 +2978,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2984,7 +2988,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,19 +3003,23 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135325573</v>
+        <v>135326498</v>
       </c>
       <c r="B23" t="n">
         <v>91974</v>
@@ -3042,17 +3050,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619652</v>
+        <v>619590</v>
       </c>
       <c r="R23" t="n">
-        <v>7322003</v>
+        <v>7321974</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,7 +3089,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,7 +3099,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,12 +3114,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3122,7 +3130,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135326358</v>
+        <v>135330914</v>
       </c>
       <c r="B24" t="n">
         <v>91974</v>
@@ -3153,17 +3161,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619562</v>
+        <v>619658</v>
       </c>
       <c r="R24" t="n">
-        <v>7322050</v>
+        <v>7321989</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3192,7 +3200,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3202,7 +3210,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3217,12 +3225,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3233,7 +3241,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135326498</v>
+        <v>135330915</v>
       </c>
       <c r="B25" t="n">
         <v>91974</v>
@@ -3264,17 +3272,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619590</v>
+        <v>619675</v>
       </c>
       <c r="R25" t="n">
-        <v>7321974</v>
+        <v>7321985</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3303,7 +3311,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3313,7 +3321,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,12 +3336,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3344,7 +3352,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135330914</v>
+        <v>135330924</v>
       </c>
       <c r="B26" t="n">
         <v>91974</v>
@@ -3379,13 +3387,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619658</v>
+        <v>619608</v>
       </c>
       <c r="R26" t="n">
-        <v>7321989</v>
+        <v>7322117</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3414,7 +3422,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3424,7 +3432,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,45 +3463,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135330915</v>
+        <v>135321343</v>
       </c>
       <c r="B27" t="n">
-        <v>91974</v>
+        <v>91988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619675</v>
+        <v>619549</v>
       </c>
       <c r="R27" t="n">
-        <v>7321985</v>
+        <v>7322014</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3525,7 +3533,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,7 +3543,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3550,12 +3558,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3566,48 +3574,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135330924</v>
+        <v>135329804</v>
       </c>
       <c r="B28" t="n">
-        <v>91974</v>
+        <v>91988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619608</v>
+        <v>619573</v>
       </c>
       <c r="R28" t="n">
-        <v>7322117</v>
+        <v>7322042</v>
       </c>
       <c r="S28" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3636,7 +3644,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3646,7 +3654,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3661,12 +3674,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3677,48 +3690,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135321343</v>
+        <v>135325577</v>
       </c>
       <c r="B29" t="n">
-        <v>91988</v>
+        <v>83222</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619549</v>
+        <v>619649</v>
       </c>
       <c r="R29" t="n">
-        <v>7322014</v>
+        <v>7322046</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3747,7 +3760,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3757,7 +3770,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3772,12 +3785,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3788,45 +3801,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135329804</v>
+        <v>135325579</v>
       </c>
       <c r="B30" t="n">
-        <v>91988</v>
+        <v>83222</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619573</v>
+        <v>619647</v>
       </c>
       <c r="R30" t="n">
-        <v>7322042</v>
+        <v>7322063</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3858,7 +3871,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3868,12 +3881,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Låga</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3888,12 +3896,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3904,7 +3912,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135325577</v>
+        <v>135325586</v>
       </c>
       <c r="B31" t="n">
         <v>83222</v>
@@ -3939,13 +3947,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>619649</v>
+        <v>619561</v>
       </c>
       <c r="R31" t="n">
-        <v>7322046</v>
+        <v>7322179</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3974,7 +3982,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3984,7 +3992,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4015,7 +4023,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135325579</v>
+        <v>135326499</v>
       </c>
       <c r="B32" t="n">
         <v>83222</v>
@@ -4046,17 +4054,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>619647</v>
+        <v>619565</v>
       </c>
       <c r="R32" t="n">
-        <v>7322063</v>
+        <v>7322000</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4085,7 +4093,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4095,7 +4103,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4110,12 +4118,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4126,45 +4134,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135325586</v>
+        <v>135323535</v>
       </c>
       <c r="B33" t="n">
-        <v>83222</v>
+        <v>92318</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>619561</v>
+        <v>619571</v>
       </c>
       <c r="R33" t="n">
-        <v>7322179</v>
+        <v>7322010</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4196,7 +4204,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4206,7 +4214,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4217,30 +4225,46 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135326499</v>
+        <v>135323533</v>
       </c>
       <c r="B34" t="n">
-        <v>83222</v>
+        <v>91896</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,37 +4272,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>3242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619565</v>
+        <v>619556</v>
       </c>
       <c r="R34" t="n">
-        <v>7322000</v>
+        <v>7322012</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4307,7 +4331,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4317,7 +4341,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4328,65 +4352,81 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135323535</v>
+        <v>135322200</v>
       </c>
       <c r="B35" t="n">
-        <v>92318</v>
+        <v>91937</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>619571</v>
+        <v>619552</v>
       </c>
       <c r="R35" t="n">
-        <v>7322010</v>
+        <v>7322009</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4418,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4428,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4439,84 +4479,68 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135323533</v>
+        <v>135322204</v>
       </c>
       <c r="B36" t="n">
-        <v>91896</v>
+        <v>91937</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>619556</v>
+        <v>619650</v>
       </c>
       <c r="R36" t="n">
-        <v>7322012</v>
+        <v>7322160</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4545,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4555,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4566,43 +4590,27 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135322200</v>
+        <v>135323531</v>
       </c>
       <c r="B37" t="n">
         <v>91937</v>
@@ -4633,17 +4641,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>619552</v>
+        <v>619624</v>
       </c>
       <c r="R37" t="n">
-        <v>7322009</v>
+        <v>7322025</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4672,7 +4680,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4682,7 +4690,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4697,61 +4705,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135322204</v>
+        <v>135325580</v>
       </c>
       <c r="B38" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>619650</v>
+        <v>619647</v>
       </c>
       <c r="R38" t="n">
-        <v>7322160</v>
+        <v>7322062</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4783,7 +4787,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4793,7 +4797,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4808,12 +4812,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4824,48 +4828,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135323531</v>
+        <v>135325595</v>
       </c>
       <c r="B39" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>619624</v>
+        <v>619537</v>
       </c>
       <c r="R39" t="n">
-        <v>7322025</v>
+        <v>7322086</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4894,7 +4898,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4904,7 +4908,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4919,60 +4923,64 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135325580</v>
+        <v>135326505</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79397</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>619647</v>
+        <v>619507</v>
       </c>
       <c r="R40" t="n">
-        <v>7322062</v>
+        <v>7322024</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5001,7 +5009,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5011,7 +5019,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5026,12 +5034,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5042,45 +5050,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135325595</v>
+        <v>135321361</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>78776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619537</v>
+        <v>619595</v>
       </c>
       <c r="R41" t="n">
-        <v>7322086</v>
+        <v>7322144</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5112,7 +5120,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5122,7 +5130,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5137,12 +5145,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5153,48 +5161,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135326505</v>
+        <v>135321364</v>
       </c>
       <c r="B42" t="n">
-        <v>79397</v>
+        <v>78776</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>619507</v>
+        <v>619580</v>
       </c>
       <c r="R42" t="n">
-        <v>7322024</v>
+        <v>7322118</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5223,7 +5231,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5233,7 +5241,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5248,12 +5256,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5264,7 +5272,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135321361</v>
+        <v>135323135</v>
       </c>
       <c r="B43" t="n">
         <v>78776</v>
@@ -5295,14 +5303,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>619595</v>
+        <v>619656</v>
       </c>
       <c r="R43" t="n">
-        <v>7322144</v>
+        <v>7322137</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5334,7 +5342,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5344,7 +5352,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5359,12 +5367,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5375,7 +5383,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135321364</v>
+        <v>135323142</v>
       </c>
       <c r="B44" t="n">
         <v>78776</v>
@@ -5406,17 +5414,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>619580</v>
+        <v>619605</v>
       </c>
       <c r="R44" t="n">
-        <v>7322118</v>
+        <v>7322191</v>
       </c>
       <c r="S44" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5445,7 +5453,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5455,7 +5463,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5470,12 +5478,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5486,7 +5494,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135323135</v>
+        <v>135323144</v>
       </c>
       <c r="B45" t="n">
         <v>78776</v>
@@ -5521,10 +5529,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>619656</v>
+        <v>619545</v>
       </c>
       <c r="R45" t="n">
-        <v>7322137</v>
+        <v>7322155</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5556,7 +5564,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5566,7 +5574,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5597,7 +5605,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135323142</v>
+        <v>135325583</v>
       </c>
       <c r="B46" t="n">
         <v>78776</v>
@@ -5628,17 +5636,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>619605</v>
+        <v>619639</v>
       </c>
       <c r="R46" t="n">
-        <v>7322191</v>
+        <v>7322093</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5667,7 +5675,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5677,7 +5685,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5692,12 +5700,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5708,7 +5716,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135323144</v>
+        <v>135326502</v>
       </c>
       <c r="B47" t="n">
         <v>78776</v>
@@ -5743,13 +5751,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>619545</v>
+        <v>619511</v>
       </c>
       <c r="R47" t="n">
-        <v>7322155</v>
+        <v>7322024</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5778,7 +5786,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5788,7 +5796,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5803,12 +5811,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5819,7 +5827,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135325583</v>
+        <v>135329821</v>
       </c>
       <c r="B48" t="n">
         <v>78776</v>
@@ -5850,14 +5858,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>619639</v>
+        <v>619634</v>
       </c>
       <c r="R48" t="n">
-        <v>7322093</v>
+        <v>7321974</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5889,7 +5897,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5899,7 +5907,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5914,12 +5922,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5930,7 +5938,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135326502</v>
+        <v>135329832</v>
       </c>
       <c r="B49" t="n">
         <v>78776</v>
@@ -5961,14 +5969,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>619511</v>
+        <v>619546</v>
       </c>
       <c r="R49" t="n">
-        <v>7322024</v>
+        <v>7322084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6000,7 +6008,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6010,7 +6018,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,12 +6033,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6041,7 +6049,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135329821</v>
+        <v>135330930</v>
       </c>
       <c r="B50" t="n">
         <v>78776</v>
@@ -6072,17 +6080,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619634</v>
+        <v>619612</v>
       </c>
       <c r="R50" t="n">
-        <v>7321974</v>
+        <v>7322185</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6111,7 +6119,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6121,7 +6129,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,12 +6144,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6152,10 +6160,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135329832</v>
+        <v>135323129</v>
       </c>
       <c r="B51" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6163,37 +6171,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>619546</v>
+        <v>619604</v>
       </c>
       <c r="R51" t="n">
-        <v>7322084</v>
+        <v>7322043</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6222,7 +6230,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6232,7 +6240,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6247,12 +6255,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6263,10 +6271,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135330930</v>
+        <v>135325571</v>
       </c>
       <c r="B52" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6274,37 +6282,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>619612</v>
+        <v>619631</v>
       </c>
       <c r="R52" t="n">
-        <v>7322185</v>
+        <v>7322000</v>
       </c>
       <c r="S52" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6333,7 +6341,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6343,7 +6351,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6358,12 +6366,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6374,7 +6382,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135323129</v>
+        <v>135325584</v>
       </c>
       <c r="B53" t="n">
         <v>83358</v>
@@ -6405,17 +6413,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>619604</v>
+        <v>619575</v>
       </c>
       <c r="R53" t="n">
-        <v>7322043</v>
+        <v>7322155</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6444,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6454,7 +6462,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6469,12 +6477,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6485,7 +6493,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135325571</v>
+        <v>135325589</v>
       </c>
       <c r="B54" t="n">
         <v>83358</v>
@@ -6520,10 +6528,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>619631</v>
+        <v>619490</v>
       </c>
       <c r="R54" t="n">
-        <v>7322000</v>
+        <v>7322171</v>
       </c>
       <c r="S54" t="n">
         <v>6</v>
@@ -6555,7 +6563,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6565,7 +6573,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6596,10 +6604,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135325584</v>
+        <v>135321549</v>
       </c>
       <c r="B55" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6607,37 +6615,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>619575</v>
+        <v>619576</v>
       </c>
       <c r="R55" t="n">
-        <v>7322155</v>
+        <v>7322127</v>
       </c>
       <c r="S55" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6666,7 +6674,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6676,7 +6684,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6691,12 +6699,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6707,10 +6715,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135325589</v>
+        <v>135322202</v>
       </c>
       <c r="B56" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6718,37 +6726,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>619490</v>
+        <v>619550</v>
       </c>
       <c r="R56" t="n">
-        <v>7322171</v>
+        <v>7322004</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6777,7 +6785,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6787,7 +6795,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6802,12 +6810,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6818,7 +6826,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135321549</v>
+        <v>135322205</v>
       </c>
       <c r="B57" t="n">
         <v>79992</v>
@@ -6849,17 +6857,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>619576</v>
+        <v>619648</v>
       </c>
       <c r="R57" t="n">
-        <v>7322127</v>
+        <v>7322202</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6888,7 +6896,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6898,7 +6906,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6913,12 +6921,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6929,7 +6937,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135322202</v>
+        <v>135323132</v>
       </c>
       <c r="B58" t="n">
         <v>79992</v>
@@ -6960,17 +6968,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>619550</v>
+        <v>619609</v>
       </c>
       <c r="R58" t="n">
-        <v>7322004</v>
+        <v>7322073</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6999,7 +7007,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7009,7 +7017,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7024,12 +7032,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7040,7 +7048,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135322205</v>
+        <v>135323145</v>
       </c>
       <c r="B59" t="n">
         <v>79992</v>
@@ -7071,17 +7079,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>619648</v>
+        <v>619557</v>
       </c>
       <c r="R59" t="n">
-        <v>7322202</v>
+        <v>7322144</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7110,7 +7118,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7120,7 +7128,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7135,12 +7143,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7151,7 +7159,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135323132</v>
+        <v>135325572</v>
       </c>
       <c r="B60" t="n">
         <v>79992</v>
@@ -7182,17 +7190,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>619609</v>
+        <v>619648</v>
       </c>
       <c r="R60" t="n">
-        <v>7322073</v>
+        <v>7321997</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7221,7 +7229,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7231,7 +7239,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7246,12 +7254,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7262,7 +7270,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135323145</v>
+        <v>135325594</v>
       </c>
       <c r="B61" t="n">
         <v>79992</v>
@@ -7293,17 +7301,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>619557</v>
+        <v>619516</v>
       </c>
       <c r="R61" t="n">
-        <v>7322144</v>
+        <v>7322084</v>
       </c>
       <c r="S61" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7332,7 +7340,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7342,7 +7350,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7357,12 +7365,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7373,7 +7381,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135325572</v>
+        <v>135326504</v>
       </c>
       <c r="B62" t="n">
         <v>79992</v>
@@ -7404,17 +7412,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>619648</v>
+        <v>619507</v>
       </c>
       <c r="R62" t="n">
-        <v>7321997</v>
+        <v>7322024</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7443,7 +7451,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7453,7 +7461,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7468,12 +7476,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7484,7 +7492,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135325594</v>
+        <v>135329819</v>
       </c>
       <c r="B63" t="n">
         <v>79992</v>
@@ -7515,17 +7523,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>619516</v>
+        <v>619650</v>
       </c>
       <c r="R63" t="n">
-        <v>7322084</v>
+        <v>7321988</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7554,7 +7562,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7564,7 +7572,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7579,12 +7587,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7595,7 +7603,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135326504</v>
+        <v>135329831</v>
       </c>
       <c r="B64" t="n">
         <v>79992</v>
@@ -7626,14 +7634,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>619507</v>
+        <v>619545</v>
       </c>
       <c r="R64" t="n">
-        <v>7322024</v>
+        <v>7322092</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7665,7 +7673,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7675,7 +7683,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7690,12 +7698,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7706,45 +7714,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135329819</v>
+        <v>135325590</v>
       </c>
       <c r="B65" t="n">
-        <v>79992</v>
+        <v>80500</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>619650</v>
+        <v>619458</v>
       </c>
       <c r="R65" t="n">
-        <v>7321988</v>
+        <v>7322119</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7776,7 +7784,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7786,7 +7794,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7801,12 +7809,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7817,10 +7825,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135329831</v>
+        <v>135321366</v>
       </c>
       <c r="B66" t="n">
-        <v>79992</v>
+        <v>78377</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7828,21 +7836,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7852,13 +7860,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>619545</v>
+        <v>619580</v>
       </c>
       <c r="R66" t="n">
-        <v>7322092</v>
+        <v>7322117</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7887,7 +7895,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7897,7 +7905,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7912,12 +7920,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7928,48 +7936,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135325590</v>
+        <v>135323134</v>
       </c>
       <c r="B67" t="n">
-        <v>80500</v>
+        <v>78377</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619458</v>
+        <v>619656</v>
       </c>
       <c r="R67" t="n">
-        <v>7322119</v>
+        <v>7322136</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7998,7 +8006,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8008,7 +8016,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8023,12 +8031,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8039,7 +8047,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135321366</v>
+        <v>135323141</v>
       </c>
       <c r="B68" t="n">
         <v>78377</v>
@@ -8070,17 +8078,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>619580</v>
+        <v>619605</v>
       </c>
       <c r="R68" t="n">
-        <v>7322117</v>
+        <v>7322191</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8109,7 +8117,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8119,7 +8127,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8134,12 +8142,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8150,7 +8158,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135323134</v>
+        <v>135325582</v>
       </c>
       <c r="B69" t="n">
         <v>78377</v>
@@ -8181,17 +8189,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>619656</v>
+        <v>619634</v>
       </c>
       <c r="R69" t="n">
-        <v>7322136</v>
+        <v>7322092</v>
       </c>
       <c r="S69" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8220,7 +8228,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8230,7 +8238,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8245,12 +8253,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8261,7 +8269,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135323141</v>
+        <v>135326506</v>
       </c>
       <c r="B70" t="n">
         <v>78377</v>
@@ -8296,13 +8304,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>619605</v>
+        <v>619505</v>
       </c>
       <c r="R70" t="n">
-        <v>7322191</v>
+        <v>7322017</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8356,12 +8364,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8372,10 +8380,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135325582</v>
+        <v>135321369</v>
       </c>
       <c r="B71" t="n">
-        <v>78377</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8383,37 +8391,45 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619634</v>
+        <v>619598</v>
       </c>
       <c r="R71" t="n">
-        <v>7322092</v>
+        <v>7322108</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8442,7 +8458,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8452,7 +8468,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8467,12 +8488,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8483,10 +8504,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135326506</v>
+        <v>135321371</v>
       </c>
       <c r="B72" t="n">
-        <v>78377</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8494,37 +8515,45 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>619505</v>
+        <v>619575</v>
       </c>
       <c r="R72" t="n">
-        <v>7322017</v>
+        <v>7322044</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8553,7 +8582,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8563,7 +8592,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8578,12 +8612,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8594,7 +8628,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135321369</v>
+        <v>135323143</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8623,27 +8657,24 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619598</v>
+        <v>619588</v>
       </c>
       <c r="R73" t="n">
-        <v>7322108</v>
+        <v>7322173</v>
       </c>
       <c r="S73" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8672,7 +8703,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8682,12 +8713,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8702,12 +8728,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8718,7 +8744,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135321371</v>
+        <v>135323524</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8747,24 +8773,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>619575</v>
+        <v>619644</v>
       </c>
       <c r="R74" t="n">
-        <v>7322044</v>
+        <v>7321971</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8796,7 +8814,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8806,12 +8824,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8826,23 +8844,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135323143</v>
+        <v>135326508</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8873,7 +8887,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8882,13 +8896,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>619588</v>
+        <v>619441</v>
       </c>
       <c r="R75" t="n">
-        <v>7322173</v>
+        <v>7322009</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8917,7 +8931,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8927,7 +8941,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8942,12 +8961,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8958,7 +8977,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135323524</v>
+        <v>135326509</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -8987,19 +9006,24 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>619644</v>
+        <v>619463</v>
       </c>
       <c r="R76" t="n">
-        <v>7321971</v>
+        <v>7321984</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9028,7 +9052,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9038,12 +9062,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9058,19 +9082,23 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135326508</v>
+        <v>135326510</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -9101,7 +9129,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9110,10 +9138,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>619441</v>
+        <v>619498</v>
       </c>
       <c r="R77" t="n">
-        <v>7322009</v>
+        <v>7321987</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9145,7 +9173,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9155,12 +9183,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9191,7 +9219,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135326509</v>
+        <v>135329836</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9220,21 +9248,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>619463</v>
+        <v>619599</v>
       </c>
       <c r="R78" t="n">
-        <v>7321984</v>
+        <v>7321991</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9266,7 +9289,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9276,12 +9299,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9296,12 +9319,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9312,7 +9335,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135326510</v>
+        <v>135330913</v>
       </c>
       <c r="B79" t="n">
         <v>57975</v>
@@ -9341,24 +9364,27 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>619498</v>
+        <v>619674</v>
       </c>
       <c r="R79" t="n">
-        <v>7321987</v>
+        <v>7321952</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9387,7 +9413,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9397,12 +9423,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9417,12 +9443,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9433,7 +9459,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135329836</v>
+        <v>135330918</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -9462,19 +9488,27 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619599</v>
+        <v>619657</v>
       </c>
       <c r="R80" t="n">
-        <v>7321991</v>
+        <v>7322019</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9503,7 +9537,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9513,12 +9547,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9533,12 +9567,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9549,7 +9583,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135330913</v>
+        <v>135330920</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -9592,13 +9626,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619674</v>
+        <v>619636</v>
       </c>
       <c r="R81" t="n">
-        <v>7321952</v>
+        <v>7322057</v>
       </c>
       <c r="S81" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9627,7 +9661,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9637,12 +9671,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Spår från födosök</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9673,7 +9707,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135330918</v>
+        <v>135330921</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -9706,7 +9740,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -9716,13 +9750,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619657</v>
+        <v>619615</v>
       </c>
       <c r="R82" t="n">
-        <v>7322019</v>
+        <v>7322104</v>
       </c>
       <c r="S82" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9751,7 +9785,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9761,12 +9795,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9797,7 +9831,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135330920</v>
+        <v>135330922</v>
       </c>
       <c r="B83" t="n">
         <v>57975</v>
@@ -9830,7 +9864,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -9840,13 +9874,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>619636</v>
+        <v>619616</v>
       </c>
       <c r="R83" t="n">
-        <v>7322057</v>
+        <v>7322103</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9875,7 +9909,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9885,12 +9919,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Spår från födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9921,7 +9955,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135330921</v>
+        <v>135330925</v>
       </c>
       <c r="B84" t="n">
         <v>57975</v>
@@ -9954,7 +9988,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -9964,13 +9998,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>619615</v>
+        <v>619617</v>
       </c>
       <c r="R84" t="n">
-        <v>7322104</v>
+        <v>7322138</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9999,7 +10033,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10009,12 +10043,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10045,7 +10079,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135330922</v>
+        <v>135330926</v>
       </c>
       <c r="B85" t="n">
         <v>57975</v>
@@ -10078,7 +10112,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -10088,13 +10122,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>619616</v>
+        <v>619652</v>
       </c>
       <c r="R85" t="n">
-        <v>7322103</v>
+        <v>7322160</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10123,7 +10157,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10133,12 +10167,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10169,7 +10203,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135330925</v>
+        <v>135330929</v>
       </c>
       <c r="B86" t="n">
         <v>57975</v>
@@ -10202,7 +10236,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10212,13 +10246,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>619617</v>
+        <v>619619</v>
       </c>
       <c r="R86" t="n">
-        <v>7322138</v>
+        <v>7322169</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10247,7 +10281,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10257,12 +10291,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10293,7 +10327,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135330926</v>
+        <v>135330931</v>
       </c>
       <c r="B87" t="n">
         <v>57975</v>
@@ -10326,7 +10360,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -10336,13 +10370,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>619652</v>
+        <v>619590</v>
       </c>
       <c r="R87" t="n">
-        <v>7322160</v>
+        <v>7322174</v>
       </c>
       <c r="S87" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10371,7 +10405,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10381,12 +10415,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10417,7 +10451,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135330929</v>
+        <v>135330935</v>
       </c>
       <c r="B88" t="n">
         <v>57975</v>
@@ -10450,7 +10484,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -10460,13 +10494,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>619619</v>
+        <v>619577</v>
       </c>
       <c r="R88" t="n">
-        <v>7322169</v>
+        <v>7322144</v>
       </c>
       <c r="S88" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10495,7 +10529,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10505,12 +10539,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10541,7 +10575,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135330931</v>
+        <v>135330936</v>
       </c>
       <c r="B89" t="n">
         <v>57975</v>
@@ -10584,13 +10618,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>619590</v>
+        <v>619598</v>
       </c>
       <c r="R89" t="n">
-        <v>7322174</v>
+        <v>7322107</v>
       </c>
       <c r="S89" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10619,7 +10653,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10629,7 +10663,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10665,7 +10699,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135330935</v>
+        <v>135330938</v>
       </c>
       <c r="B90" t="n">
         <v>57975</v>
@@ -10708,13 +10742,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>619577</v>
+        <v>619571</v>
       </c>
       <c r="R90" t="n">
-        <v>7322144</v>
+        <v>7322045</v>
       </c>
       <c r="S90" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10743,7 +10777,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10753,7 +10787,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10789,56 +10823,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135330936</v>
+        <v>135325591</v>
       </c>
       <c r="B91" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>619598</v>
+        <v>619449</v>
       </c>
       <c r="R91" t="n">
-        <v>7322107</v>
+        <v>7322120</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10867,7 +10893,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10877,12 +10903,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10897,12 +10918,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10913,10 +10934,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135330938</v>
+        <v>135323146</v>
       </c>
       <c r="B92" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,45 +10945,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>619571</v>
+        <v>619591</v>
       </c>
       <c r="R92" t="n">
-        <v>7322045</v>
+        <v>7322093</v>
       </c>
       <c r="S92" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10991,7 +11004,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11001,12 +11014,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11021,12 +11029,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11037,48 +11045,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135325591</v>
+        <v>135323532</v>
       </c>
       <c r="B93" t="n">
-        <v>57162</v>
+        <v>58136</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>619449</v>
+        <v>619540</v>
       </c>
       <c r="R93" t="n">
-        <v>7322120</v>
+        <v>7322034</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11107,7 +11115,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11117,7 +11125,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11132,23 +11140,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135323146</v>
+        <v>135325587</v>
       </c>
       <c r="B94" t="n">
         <v>58136</v>
@@ -11179,17 +11183,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>619591</v>
+        <v>619517</v>
       </c>
       <c r="R94" t="n">
-        <v>7322093</v>
+        <v>7322182</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11218,7 +11222,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11228,7 +11232,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11243,12 +11247,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11259,7 +11263,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135323532</v>
+        <v>135326500</v>
       </c>
       <c r="B95" t="n">
         <v>58136</v>
@@ -11287,20 +11291,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>619540</v>
+        <v>619528</v>
       </c>
       <c r="R95" t="n">
-        <v>7322034</v>
+        <v>7322006</v>
       </c>
       <c r="S95" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11329,7 +11342,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11339,7 +11352,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11354,19 +11367,23 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135325587</v>
+        <v>135330933</v>
       </c>
       <c r="B96" t="n">
         <v>58136</v>
@@ -11395,19 +11412,27 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>619517</v>
+        <v>619580</v>
       </c>
       <c r="R96" t="n">
-        <v>7322182</v>
+        <v>7322161</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11461,12 +11486,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11477,7 +11502,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135326500</v>
+        <v>135330937</v>
       </c>
       <c r="B97" t="n">
         <v>58136</v>
@@ -11505,29 +11530,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>619528</v>
+        <v>619572</v>
       </c>
       <c r="R97" t="n">
-        <v>7322006</v>
+        <v>7322048</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11556,7 +11580,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11566,7 +11590,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11581,12 +11605,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11597,10 +11621,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135330933</v>
+        <v>135321349</v>
       </c>
       <c r="B98" t="n">
-        <v>58136</v>
+        <v>78382</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11608,45 +11632,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>619580</v>
+        <v>619627</v>
       </c>
       <c r="R98" t="n">
-        <v>7322161</v>
+        <v>7322118</v>
       </c>
       <c r="S98" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11675,7 +11691,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11685,7 +11701,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11700,12 +11716,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11716,10 +11732,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135330937</v>
+        <v>135323128</v>
       </c>
       <c r="B99" t="n">
-        <v>58136</v>
+        <v>78382</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11727,45 +11743,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>619572</v>
+        <v>619549</v>
       </c>
       <c r="R99" t="n">
-        <v>7322048</v>
+        <v>7322008</v>
       </c>
       <c r="S99" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11794,7 +11802,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11804,7 +11812,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11819,12 +11827,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11835,10 +11843,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135323945</v>
+        <v>135323131</v>
       </c>
       <c r="B100" t="n">
-        <v>41606</v>
+        <v>78382</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11846,42 +11854,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>215713</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>619649</v>
+        <v>619607</v>
       </c>
       <c r="R100" t="n">
-        <v>7322021</v>
+        <v>7322071</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11910,7 +11913,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11920,7 +11923,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11935,19 +11938,23 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135321349</v>
+        <v>135323133</v>
       </c>
       <c r="B101" t="n">
         <v>78382</v>
@@ -11978,17 +11985,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>619627</v>
+        <v>619624</v>
       </c>
       <c r="R101" t="n">
-        <v>7322118</v>
+        <v>7322126</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12042,12 +12049,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12058,7 +12065,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135323128</v>
+        <v>135326507</v>
       </c>
       <c r="B102" t="n">
         <v>78382</v>
@@ -12093,13 +12100,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>619549</v>
+        <v>619502</v>
       </c>
       <c r="R102" t="n">
-        <v>7322008</v>
+        <v>7322009</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12128,7 +12135,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12138,7 +12145,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12153,12 +12160,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12169,10 +12176,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135323131</v>
+        <v>135326503</v>
       </c>
       <c r="B103" t="n">
-        <v>78382</v>
+        <v>79963</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12180,21 +12187,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228579</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12204,13 +12211,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>619607</v>
+        <v>619511</v>
       </c>
       <c r="R103" t="n">
-        <v>7322071</v>
+        <v>7322024</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12239,7 +12246,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12249,7 +12256,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12264,12 +12271,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12280,10 +12287,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135323133</v>
+        <v>135321359</v>
       </c>
       <c r="B104" t="n">
-        <v>78382</v>
+        <v>79396</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12291,37 +12298,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228579</v>
+        <v>260591</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>619624</v>
+        <v>619585</v>
       </c>
       <c r="R104" t="n">
-        <v>7322126</v>
+        <v>7322120</v>
       </c>
       <c r="S104" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12350,7 +12357,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12360,7 +12367,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12375,12 +12382,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12391,10 +12398,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135326507</v>
+        <v>135323530</v>
       </c>
       <c r="B105" t="n">
-        <v>78382</v>
+        <v>79396</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12402,37 +12409,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228579</v>
+        <v>260591</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>619502</v>
+        <v>619609</v>
       </c>
       <c r="R105" t="n">
-        <v>7322009</v>
+        <v>7322000</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12461,7 +12468,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12471,7 +12478,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12486,26 +12493,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135326503</v>
+        <v>135329830</v>
       </c>
       <c r="B106" t="n">
-        <v>79963</v>
+        <v>79396</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,34 +12516,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>619511</v>
+        <v>619599</v>
       </c>
       <c r="R106" t="n">
-        <v>7322024</v>
+        <v>7322098</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12572,7 +12575,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12582,7 +12585,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12597,12 +12600,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12613,10 +12616,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135321359</v>
+        <v>135323529</v>
       </c>
       <c r="B107" t="n">
-        <v>79396</v>
+        <v>92366</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12624,37 +12627,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>260591</v>
+        <v>6040186</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>619585</v>
+        <v>619629</v>
       </c>
       <c r="R107" t="n">
-        <v>7322120</v>
+        <v>7321999</v>
       </c>
       <c r="S107" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12683,7 +12686,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12693,7 +12696,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12702,371 +12705,42 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>135323530</v>
-      </c>
-      <c r="B108" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q108" t="n">
-        <v>619609</v>
-      </c>
-      <c r="R108" t="n">
-        <v>7322000</v>
-      </c>
-      <c r="S108" t="n">
-        <v>7</v>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AD108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT108" t="inlineStr"/>
-      <c r="AW108" t="inlineStr">
-        <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>135329830</v>
-      </c>
-      <c r="B109" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q109" t="n">
-        <v>619599</v>
-      </c>
-      <c r="R109" t="n">
-        <v>7322098</v>
-      </c>
-      <c r="S109" t="n">
-        <v>10</v>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AD109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT109" t="inlineStr"/>
-      <c r="AW109" t="inlineStr">
-        <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>135323529</v>
-      </c>
-      <c r="B110" t="n">
-        <v>92366</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q110" t="n">
-        <v>619629</v>
-      </c>
-      <c r="R110" t="n">
-        <v>7321999</v>
-      </c>
-      <c r="S110" t="n">
-        <v>7</v>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AD110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF110" t="inlineStr"/>
-      <c r="AG110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT110" t="inlineStr"/>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+      <c r="AY107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8380,7 +8380,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135321369</v>
+        <v>135323143</v>
       </c>
       <c r="B71" t="n">
         <v>57975</v>
@@ -8409,27 +8409,24 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619598</v>
+        <v>619588</v>
       </c>
       <c r="R71" t="n">
-        <v>7322108</v>
+        <v>7322173</v>
       </c>
       <c r="S71" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8458,7 +8455,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8468,12 +8465,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8488,12 +8480,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8504,7 +8496,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135321371</v>
+        <v>135323524</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -8533,24 +8525,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>619575</v>
+        <v>619644</v>
       </c>
       <c r="R72" t="n">
-        <v>7322044</v>
+        <v>7321971</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8582,7 +8566,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8592,12 +8576,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8612,23 +8596,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135323143</v>
+        <v>135326508</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8659,7 +8639,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8668,13 +8648,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619588</v>
+        <v>619441</v>
       </c>
       <c r="R73" t="n">
-        <v>7322173</v>
+        <v>7322009</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8703,7 +8683,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8713,7 +8693,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8728,12 +8713,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8744,7 +8729,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135323524</v>
+        <v>135326509</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8773,19 +8758,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>619644</v>
+        <v>619463</v>
       </c>
       <c r="R74" t="n">
-        <v>7321971</v>
+        <v>7321984</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8814,7 +8804,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8824,12 +8814,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8844,19 +8834,23 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135326508</v>
+        <v>135326510</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8887,7 +8881,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8896,10 +8890,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>619441</v>
+        <v>619498</v>
       </c>
       <c r="R75" t="n">
-        <v>7322009</v>
+        <v>7321987</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8931,7 +8925,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8941,12 +8935,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8977,7 +8971,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135326509</v>
+        <v>135329836</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -9006,21 +9000,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>619463</v>
+        <v>619599</v>
       </c>
       <c r="R76" t="n">
-        <v>7321984</v>
+        <v>7321991</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9052,7 +9041,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9062,12 +9051,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9082,12 +9071,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9098,7 +9087,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135326510</v>
+        <v>135330913</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -9127,24 +9116,27 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>619498</v>
+        <v>619674</v>
       </c>
       <c r="R77" t="n">
-        <v>7321987</v>
+        <v>7321952</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9173,7 +9165,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9183,12 +9175,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9203,12 +9195,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9219,7 +9211,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135329836</v>
+        <v>135330918</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9248,19 +9240,27 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>619599</v>
+        <v>619657</v>
       </c>
       <c r="R78" t="n">
-        <v>7321991</v>
+        <v>7322019</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9319,12 +9319,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9335,7 +9335,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135330913</v>
+        <v>135330920</v>
       </c>
       <c r="B79" t="n">
         <v>57975</v>
@@ -9378,13 +9378,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>619674</v>
+        <v>619636</v>
       </c>
       <c r="R79" t="n">
-        <v>7321952</v>
+        <v>7322057</v>
       </c>
       <c r="S79" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Spår från födosök</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9459,7 +9459,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135330918</v>
+        <v>135330921</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -9492,7 +9492,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9502,13 +9502,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619657</v>
+        <v>619615</v>
       </c>
       <c r="R80" t="n">
-        <v>7322019</v>
+        <v>7322104</v>
       </c>
       <c r="S80" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9547,12 +9547,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9583,7 +9583,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135330920</v>
+        <v>135330922</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -9616,7 +9616,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9626,13 +9626,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619636</v>
+        <v>619616</v>
       </c>
       <c r="R81" t="n">
-        <v>7322057</v>
+        <v>7322103</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Spår från födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9707,7 +9707,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135330921</v>
+        <v>135330925</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -9740,7 +9740,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -9750,13 +9750,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619615</v>
+        <v>619617</v>
       </c>
       <c r="R82" t="n">
-        <v>7322104</v>
+        <v>7322138</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9831,7 +9831,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135330922</v>
+        <v>135330926</v>
       </c>
       <c r="B83" t="n">
         <v>57975</v>
@@ -9864,7 +9864,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -9874,13 +9874,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>619616</v>
+        <v>619652</v>
       </c>
       <c r="R83" t="n">
-        <v>7322103</v>
+        <v>7322160</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9955,7 +9955,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135330925</v>
+        <v>135330929</v>
       </c>
       <c r="B84" t="n">
         <v>57975</v>
@@ -9988,7 +9988,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>619617</v>
+        <v>619619</v>
       </c>
       <c r="R84" t="n">
-        <v>7322138</v>
+        <v>7322169</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10043,12 +10043,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10079,7 +10079,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135330926</v>
+        <v>135330931</v>
       </c>
       <c r="B85" t="n">
         <v>57975</v>
@@ -10112,7 +10112,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -10122,13 +10122,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>619652</v>
+        <v>619590</v>
       </c>
       <c r="R85" t="n">
-        <v>7322160</v>
+        <v>7322174</v>
       </c>
       <c r="S85" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10203,7 +10203,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135330929</v>
+        <v>135330935</v>
       </c>
       <c r="B86" t="n">
         <v>57975</v>
@@ -10236,7 +10236,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10246,13 +10246,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>619619</v>
+        <v>619577</v>
       </c>
       <c r="R86" t="n">
-        <v>7322169</v>
+        <v>7322144</v>
       </c>
       <c r="S86" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10327,7 +10327,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135330931</v>
+        <v>135330936</v>
       </c>
       <c r="B87" t="n">
         <v>57975</v>
@@ -10370,13 +10370,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>619590</v>
+        <v>619598</v>
       </c>
       <c r="R87" t="n">
-        <v>7322174</v>
+        <v>7322107</v>
       </c>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10451,7 +10451,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135330935</v>
+        <v>135330938</v>
       </c>
       <c r="B88" t="n">
         <v>57975</v>
@@ -10494,13 +10494,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>619577</v>
+        <v>619571</v>
       </c>
       <c r="R88" t="n">
-        <v>7322144</v>
+        <v>7322045</v>
       </c>
       <c r="S88" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10575,56 +10575,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135330936</v>
+        <v>135325591</v>
       </c>
       <c r="B89" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>619598</v>
+        <v>619449</v>
       </c>
       <c r="R89" t="n">
-        <v>7322107</v>
+        <v>7322120</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10653,7 +10645,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10663,12 +10655,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10683,12 +10670,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10699,10 +10686,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135330938</v>
+        <v>135323146</v>
       </c>
       <c r="B90" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10710,45 +10697,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>619571</v>
+        <v>619591</v>
       </c>
       <c r="R90" t="n">
-        <v>7322045</v>
+        <v>7322093</v>
       </c>
       <c r="S90" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10777,7 +10756,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10787,12 +10766,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10807,12 +10781,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10823,48 +10797,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135325591</v>
+        <v>135323532</v>
       </c>
       <c r="B91" t="n">
-        <v>57162</v>
+        <v>58136</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>619449</v>
+        <v>619540</v>
       </c>
       <c r="R91" t="n">
-        <v>7322120</v>
+        <v>7322034</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10893,7 +10867,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10903,7 +10877,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10918,23 +10892,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135323146</v>
+        <v>135325587</v>
       </c>
       <c r="B92" t="n">
         <v>58136</v>
@@ -10965,17 +10935,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>619591</v>
+        <v>619517</v>
       </c>
       <c r="R92" t="n">
-        <v>7322093</v>
+        <v>7322182</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11004,7 +10974,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11014,7 +10984,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11029,12 +10999,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11045,7 +11015,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135323532</v>
+        <v>135326500</v>
       </c>
       <c r="B93" t="n">
         <v>58136</v>
@@ -11073,20 +11043,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>619540</v>
+        <v>619528</v>
       </c>
       <c r="R93" t="n">
-        <v>7322034</v>
+        <v>7322006</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11115,7 +11094,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11125,7 +11104,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11140,19 +11119,23 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135325587</v>
+        <v>135330933</v>
       </c>
       <c r="B94" t="n">
         <v>58136</v>
@@ -11181,19 +11164,27 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>619517</v>
+        <v>619580</v>
       </c>
       <c r="R94" t="n">
-        <v>7322182</v>
+        <v>7322161</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11247,12 +11238,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11263,7 +11254,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135326500</v>
+        <v>135330937</v>
       </c>
       <c r="B95" t="n">
         <v>58136</v>
@@ -11291,29 +11282,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>619528</v>
+        <v>619572</v>
       </c>
       <c r="R95" t="n">
-        <v>7322006</v>
+        <v>7322048</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11342,7 +11332,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11352,7 +11342,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11367,12 +11357,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11383,10 +11373,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135330933</v>
+        <v>135321349</v>
       </c>
       <c r="B96" t="n">
-        <v>58136</v>
+        <v>78382</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11394,45 +11384,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>619580</v>
+        <v>619627</v>
       </c>
       <c r="R96" t="n">
-        <v>7322161</v>
+        <v>7322118</v>
       </c>
       <c r="S96" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11461,7 +11443,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11471,7 +11453,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11486,12 +11468,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11502,10 +11484,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135330937</v>
+        <v>135323128</v>
       </c>
       <c r="B97" t="n">
-        <v>58136</v>
+        <v>78382</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11513,45 +11495,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>619572</v>
+        <v>619549</v>
       </c>
       <c r="R97" t="n">
-        <v>7322048</v>
+        <v>7322008</v>
       </c>
       <c r="S97" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11580,7 +11554,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11590,7 +11564,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11605,12 +11579,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11621,7 +11595,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135321349</v>
+        <v>135323131</v>
       </c>
       <c r="B98" t="n">
         <v>78382</v>
@@ -11652,14 +11626,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>619627</v>
+        <v>619607</v>
       </c>
       <c r="R98" t="n">
-        <v>7322118</v>
+        <v>7322071</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11691,7 +11665,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11701,7 +11675,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11716,12 +11690,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11732,7 +11706,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135323128</v>
+        <v>135323133</v>
       </c>
       <c r="B99" t="n">
         <v>78382</v>
@@ -11767,13 +11741,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>619549</v>
+        <v>619624</v>
       </c>
       <c r="R99" t="n">
-        <v>7322008</v>
+        <v>7322126</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11802,7 +11776,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11812,7 +11786,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11843,7 +11817,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135323131</v>
+        <v>135326507</v>
       </c>
       <c r="B100" t="n">
         <v>78382</v>
@@ -11878,13 +11852,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>619607</v>
+        <v>619502</v>
       </c>
       <c r="R100" t="n">
-        <v>7322071</v>
+        <v>7322009</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11913,7 +11887,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11923,7 +11897,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11938,12 +11912,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11954,10 +11928,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135323133</v>
+        <v>135326503</v>
       </c>
       <c r="B101" t="n">
-        <v>78382</v>
+        <v>79963</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11965,21 +11939,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228579</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11989,13 +11963,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>619624</v>
+        <v>619511</v>
       </c>
       <c r="R101" t="n">
-        <v>7322126</v>
+        <v>7322024</v>
       </c>
       <c r="S101" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12024,7 +11998,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12034,7 +12008,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12049,12 +12023,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12065,10 +12039,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135326507</v>
+        <v>135323530</v>
       </c>
       <c r="B102" t="n">
-        <v>78382</v>
+        <v>79396</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12076,37 +12050,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228579</v>
+        <v>260591</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>619502</v>
+        <v>619609</v>
       </c>
       <c r="R102" t="n">
-        <v>7322009</v>
+        <v>7322000</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12135,7 +12109,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12145,7 +12119,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12160,26 +12134,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135326503</v>
+        <v>135329830</v>
       </c>
       <c r="B103" t="n">
-        <v>79963</v>
+        <v>79396</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12187,34 +12157,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>619511</v>
+        <v>619599</v>
       </c>
       <c r="R103" t="n">
-        <v>7322024</v>
+        <v>7322098</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12246,7 +12216,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12256,7 +12226,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12271,12 +12241,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12287,10 +12257,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135321359</v>
+        <v>135323529</v>
       </c>
       <c r="B104" t="n">
-        <v>79396</v>
+        <v>92366</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12298,37 +12268,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>260591</v>
+        <v>6040186</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>619585</v>
+        <v>619629</v>
       </c>
       <c r="R104" t="n">
-        <v>7322120</v>
+        <v>7321999</v>
       </c>
       <c r="S104" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12357,7 +12327,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12367,7 +12337,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12376,371 +12346,42 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>135323530</v>
-      </c>
-      <c r="B105" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q105" t="n">
-        <v>619609</v>
-      </c>
-      <c r="R105" t="n">
-        <v>7322000</v>
-      </c>
-      <c r="S105" t="n">
-        <v>7</v>
-      </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AD105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT105" t="inlineStr"/>
-      <c r="AW105" t="inlineStr">
-        <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>135329830</v>
-      </c>
-      <c r="B106" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q106" t="n">
-        <v>619599</v>
-      </c>
-      <c r="R106" t="n">
-        <v>7322098</v>
-      </c>
-      <c r="S106" t="n">
-        <v>10</v>
-      </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AD106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT106" t="inlineStr"/>
-      <c r="AW106" t="inlineStr">
-        <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>135323529</v>
-      </c>
-      <c r="B107" t="n">
-        <v>92366</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q107" t="n">
-        <v>619629</v>
-      </c>
-      <c r="R107" t="n">
-        <v>7321999</v>
-      </c>
-      <c r="S107" t="n">
-        <v>7</v>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AD107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF107" t="inlineStr"/>
-      <c r="AG107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT107" t="inlineStr"/>
-      <c r="AW107" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+      <c r="AY104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8380,7 +8380,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135323143</v>
+        <v>135321369</v>
       </c>
       <c r="B71" t="n">
         <v>57975</v>
@@ -8409,24 +8409,27 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619588</v>
+        <v>619598</v>
       </c>
       <c r="R71" t="n">
-        <v>7322173</v>
+        <v>7322108</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8455,7 +8458,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8465,7 +8468,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8480,12 +8488,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8496,7 +8504,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135323524</v>
+        <v>135321371</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -8525,16 +8533,24 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>619644</v>
+        <v>619575</v>
       </c>
       <c r="R72" t="n">
-        <v>7321971</v>
+        <v>7322044</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8566,7 +8582,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8576,12 +8592,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8596,19 +8612,23 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135326508</v>
+        <v>135323143</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8639,7 +8659,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8648,13 +8668,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619441</v>
+        <v>619588</v>
       </c>
       <c r="R73" t="n">
-        <v>7322009</v>
+        <v>7322173</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8683,7 +8703,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8693,12 +8713,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8713,12 +8728,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8729,7 +8744,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135326509</v>
+        <v>135323524</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8758,24 +8773,19 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>619463</v>
+        <v>619644</v>
       </c>
       <c r="R74" t="n">
-        <v>7321984</v>
+        <v>7321971</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8804,7 +8814,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8814,12 +8824,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8834,23 +8844,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135326510</v>
+        <v>135326508</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8881,7 +8887,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8890,10 +8896,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>619498</v>
+        <v>619441</v>
       </c>
       <c r="R75" t="n">
-        <v>7321987</v>
+        <v>7322009</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8925,7 +8931,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8935,12 +8941,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8971,7 +8977,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135329836</v>
+        <v>135326509</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -9000,16 +9006,21 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>619599</v>
+        <v>619463</v>
       </c>
       <c r="R76" t="n">
-        <v>7321991</v>
+        <v>7321984</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9041,7 +9052,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9051,12 +9062,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9071,12 +9082,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9087,7 +9098,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135330913</v>
+        <v>135326510</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -9116,27 +9127,24 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>619674</v>
+        <v>619498</v>
       </c>
       <c r="R77" t="n">
-        <v>7321952</v>
+        <v>7321987</v>
       </c>
       <c r="S77" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9165,7 +9173,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9175,12 +9183,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9195,12 +9203,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9211,7 +9219,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135330918</v>
+        <v>135329836</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9240,27 +9248,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>619657</v>
+        <v>619599</v>
       </c>
       <c r="R78" t="n">
-        <v>7322019</v>
+        <v>7321991</v>
       </c>
       <c r="S78" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9319,12 +9319,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9335,7 +9335,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135330920</v>
+        <v>135330913</v>
       </c>
       <c r="B79" t="n">
         <v>57975</v>
@@ -9378,13 +9378,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>619636</v>
+        <v>619674</v>
       </c>
       <c r="R79" t="n">
-        <v>7322057</v>
+        <v>7321952</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Spår från födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9459,7 +9459,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135330921</v>
+        <v>135330918</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -9492,7 +9492,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9502,13 +9502,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619615</v>
+        <v>619657</v>
       </c>
       <c r="R80" t="n">
-        <v>7322104</v>
+        <v>7322019</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9547,12 +9547,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9583,7 +9583,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135330922</v>
+        <v>135330920</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -9616,7 +9616,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9626,13 +9626,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619616</v>
+        <v>619636</v>
       </c>
       <c r="R81" t="n">
-        <v>7322103</v>
+        <v>7322057</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår från födosök</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9707,7 +9707,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135330925</v>
+        <v>135330921</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -9740,7 +9740,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -9750,13 +9750,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619617</v>
+        <v>619615</v>
       </c>
       <c r="R82" t="n">
-        <v>7322138</v>
+        <v>7322104</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9831,7 +9831,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135330926</v>
+        <v>135330922</v>
       </c>
       <c r="B83" t="n">
         <v>57975</v>
@@ -9864,7 +9864,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -9874,13 +9874,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>619652</v>
+        <v>619616</v>
       </c>
       <c r="R83" t="n">
-        <v>7322160</v>
+        <v>7322103</v>
       </c>
       <c r="S83" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9955,7 +9955,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135330929</v>
+        <v>135330925</v>
       </c>
       <c r="B84" t="n">
         <v>57975</v>
@@ -9988,7 +9988,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>619619</v>
+        <v>619617</v>
       </c>
       <c r="R84" t="n">
-        <v>7322169</v>
+        <v>7322138</v>
       </c>
       <c r="S84" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10043,12 +10043,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10079,7 +10079,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135330931</v>
+        <v>135330926</v>
       </c>
       <c r="B85" t="n">
         <v>57975</v>
@@ -10112,7 +10112,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -10122,13 +10122,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>619590</v>
+        <v>619652</v>
       </c>
       <c r="R85" t="n">
-        <v>7322174</v>
+        <v>7322160</v>
       </c>
       <c r="S85" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10203,7 +10203,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135330935</v>
+        <v>135330929</v>
       </c>
       <c r="B86" t="n">
         <v>57975</v>
@@ -10236,7 +10236,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10246,13 +10246,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>619577</v>
+        <v>619619</v>
       </c>
       <c r="R86" t="n">
-        <v>7322144</v>
+        <v>7322169</v>
       </c>
       <c r="S86" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10327,7 +10327,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135330936</v>
+        <v>135330931</v>
       </c>
       <c r="B87" t="n">
         <v>57975</v>
@@ -10370,13 +10370,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>619598</v>
+        <v>619590</v>
       </c>
       <c r="R87" t="n">
-        <v>7322107</v>
+        <v>7322174</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10451,7 +10451,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135330938</v>
+        <v>135330935</v>
       </c>
       <c r="B88" t="n">
         <v>57975</v>
@@ -10494,13 +10494,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>619571</v>
+        <v>619577</v>
       </c>
       <c r="R88" t="n">
-        <v>7322045</v>
+        <v>7322144</v>
       </c>
       <c r="S88" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10575,48 +10575,56 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135325591</v>
+        <v>135330936</v>
       </c>
       <c r="B89" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>619449</v>
+        <v>619598</v>
       </c>
       <c r="R89" t="n">
-        <v>7322120</v>
+        <v>7322107</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10645,7 +10653,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10655,7 +10663,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10670,12 +10683,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10686,10 +10699,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135323146</v>
+        <v>135330938</v>
       </c>
       <c r="B90" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10697,37 +10710,45 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>619591</v>
+        <v>619571</v>
       </c>
       <c r="R90" t="n">
-        <v>7322093</v>
+        <v>7322045</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10756,7 +10777,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10766,7 +10787,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10781,12 +10807,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10797,48 +10823,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135323532</v>
+        <v>135325591</v>
       </c>
       <c r="B91" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>619540</v>
+        <v>619449</v>
       </c>
       <c r="R91" t="n">
-        <v>7322034</v>
+        <v>7322120</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10867,7 +10893,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10877,7 +10903,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10892,19 +10918,23 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135325587</v>
+        <v>135323146</v>
       </c>
       <c r="B92" t="n">
         <v>58136</v>
@@ -10935,17 +10965,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>619517</v>
+        <v>619591</v>
       </c>
       <c r="R92" t="n">
-        <v>7322182</v>
+        <v>7322093</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10974,7 +11004,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10984,7 +11014,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10999,12 +11029,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11015,7 +11045,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135326500</v>
+        <v>135323532</v>
       </c>
       <c r="B93" t="n">
         <v>58136</v>
@@ -11043,29 +11073,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>619528</v>
+        <v>619540</v>
       </c>
       <c r="R93" t="n">
-        <v>7322006</v>
+        <v>7322034</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11094,7 +11115,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11104,7 +11125,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11119,23 +11140,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135330933</v>
+        <v>135325587</v>
       </c>
       <c r="B94" t="n">
         <v>58136</v>
@@ -11164,27 +11181,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>619580</v>
+        <v>619517</v>
       </c>
       <c r="R94" t="n">
-        <v>7322161</v>
+        <v>7322182</v>
       </c>
       <c r="S94" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11238,12 +11247,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11254,7 +11263,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135330937</v>
+        <v>135326500</v>
       </c>
       <c r="B95" t="n">
         <v>58136</v>
@@ -11282,28 +11291,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>619572</v>
+        <v>619528</v>
       </c>
       <c r="R95" t="n">
-        <v>7322048</v>
+        <v>7322006</v>
       </c>
       <c r="S95" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11332,7 +11342,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11342,7 +11352,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11357,12 +11367,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11373,10 +11383,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135321349</v>
+        <v>135330933</v>
       </c>
       <c r="B96" t="n">
-        <v>78382</v>
+        <v>58136</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11384,37 +11394,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>619627</v>
+        <v>619580</v>
       </c>
       <c r="R96" t="n">
-        <v>7322118</v>
+        <v>7322161</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11443,7 +11461,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11453,7 +11471,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11468,12 +11486,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11484,10 +11502,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135323128</v>
+        <v>135330937</v>
       </c>
       <c r="B97" t="n">
-        <v>78382</v>
+        <v>58136</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11495,37 +11513,45 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>619549</v>
+        <v>619572</v>
       </c>
       <c r="R97" t="n">
-        <v>7322008</v>
+        <v>7322048</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11554,7 +11580,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11564,7 +11590,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11579,12 +11605,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11595,7 +11621,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135323131</v>
+        <v>135321349</v>
       </c>
       <c r="B98" t="n">
         <v>78382</v>
@@ -11626,14 +11652,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>619607</v>
+        <v>619627</v>
       </c>
       <c r="R98" t="n">
-        <v>7322071</v>
+        <v>7322118</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11665,7 +11691,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11675,7 +11701,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11690,12 +11716,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11706,7 +11732,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135323133</v>
+        <v>135323128</v>
       </c>
       <c r="B99" t="n">
         <v>78382</v>
@@ -11741,13 +11767,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>619624</v>
+        <v>619549</v>
       </c>
       <c r="R99" t="n">
-        <v>7322126</v>
+        <v>7322008</v>
       </c>
       <c r="S99" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11776,7 +11802,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11786,7 +11812,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11817,7 +11843,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135326507</v>
+        <v>135323131</v>
       </c>
       <c r="B100" t="n">
         <v>78382</v>
@@ -11852,13 +11878,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>619502</v>
+        <v>619607</v>
       </c>
       <c r="R100" t="n">
-        <v>7322009</v>
+        <v>7322071</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11887,7 +11913,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11897,7 +11923,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11912,12 +11938,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11928,10 +11954,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135326503</v>
+        <v>135323133</v>
       </c>
       <c r="B101" t="n">
-        <v>79963</v>
+        <v>78382</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11939,21 +11965,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11963,13 +11989,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>619511</v>
+        <v>619624</v>
       </c>
       <c r="R101" t="n">
-        <v>7322024</v>
+        <v>7322126</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11998,7 +12024,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12008,7 +12034,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12023,12 +12049,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12039,10 +12065,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135323530</v>
+        <v>135326507</v>
       </c>
       <c r="B102" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12050,37 +12076,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>619609</v>
+        <v>619502</v>
       </c>
       <c r="R102" t="n">
-        <v>7322000</v>
+        <v>7322009</v>
       </c>
       <c r="S102" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12109,7 +12135,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12119,7 +12145,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12134,22 +12160,26 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135329830</v>
+        <v>135326503</v>
       </c>
       <c r="B103" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12157,34 +12187,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>619599</v>
+        <v>619511</v>
       </c>
       <c r="R103" t="n">
-        <v>7322098</v>
+        <v>7322024</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12216,7 +12246,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12226,7 +12256,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12241,12 +12271,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12257,10 +12287,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135323529</v>
+        <v>135321359</v>
       </c>
       <c r="B104" t="n">
-        <v>92366</v>
+        <v>79396</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12268,37 +12298,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6040186</v>
+        <v>260591</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>619629</v>
+        <v>619585</v>
       </c>
       <c r="R104" t="n">
-        <v>7321999</v>
+        <v>7322120</v>
       </c>
       <c r="S104" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12327,7 +12357,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12337,7 +12367,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12346,42 +12376,371 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>135323530</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>619609</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7322000</v>
+      </c>
+      <c r="S105" t="n">
+        <v>7</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
+      <c r="AX105" t="inlineStr">
         <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AY104" t="inlineStr"/>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>135329830</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Maskaure Uddnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>619599</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7322098</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>135323529</v>
+      </c>
+      <c r="B107" t="n">
+        <v>92366</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>619629</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7321999</v>
+      </c>
+      <c r="S107" t="n">
+        <v>7</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135325593</v>
+        <v>135323935</v>
       </c>
       <c r="B2" t="n">
-        <v>79992</v>
+        <v>96678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2166</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619420</v>
+        <v>619433</v>
       </c>
       <c r="R2" t="n">
-        <v>7322107</v>
+        <v>7322100</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135325592</v>
+        <v>135325593</v>
       </c>
       <c r="B3" t="n">
-        <v>79963</v>
+        <v>79992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         <v>619420</v>
       </c>
       <c r="R3" t="n">
-        <v>7322103</v>
+        <v>7322107</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,48 +897,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135323126</v>
+        <v>135323934</v>
       </c>
       <c r="B4" t="n">
-        <v>92593</v>
+        <v>98066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619583</v>
+        <v>619430</v>
       </c>
       <c r="R4" t="n">
-        <v>7322014</v>
+        <v>7322096</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,12 +992,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135323140</v>
+        <v>135325592</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,37 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619611</v>
+        <v>619420</v>
       </c>
       <c r="R5" t="n">
-        <v>7322196</v>
+        <v>7322103</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,12 +1103,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1119,48 +1119,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135321345</v>
+        <v>135323126</v>
       </c>
       <c r="B6" t="n">
-        <v>92245</v>
+        <v>92593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619545</v>
+        <v>619583</v>
       </c>
       <c r="R6" t="n">
-        <v>7322019</v>
+        <v>7322014</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135322203</v>
+        <v>135323140</v>
       </c>
       <c r="B7" t="n">
-        <v>92245</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,37 +1241,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619565</v>
+        <v>619611</v>
       </c>
       <c r="R7" t="n">
-        <v>7322022</v>
+        <v>7322196</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135323127</v>
+        <v>135321345</v>
       </c>
       <c r="B8" t="n">
         <v>92245</v>
@@ -1372,14 +1372,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619583</v>
+        <v>619545</v>
       </c>
       <c r="R8" t="n">
-        <v>7322014</v>
+        <v>7322019</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,12 +1436,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135323130</v>
+        <v>135322203</v>
       </c>
       <c r="B9" t="n">
         <v>92245</v>
@@ -1483,17 +1483,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619604</v>
+        <v>619565</v>
       </c>
       <c r="R9" t="n">
-        <v>7322053</v>
+        <v>7322022</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,12 +1547,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135323526</v>
+        <v>135323127</v>
       </c>
       <c r="B10" t="n">
         <v>92245</v>
@@ -1594,14 +1594,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619613</v>
+        <v>619583</v>
       </c>
       <c r="R10" t="n">
-        <v>7321994</v>
+        <v>7322014</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,19 +1658,23 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135323528</v>
+        <v>135323130</v>
       </c>
       <c r="B11" t="n">
         <v>92245</v>
@@ -1701,17 +1705,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619630</v>
+        <v>619604</v>
       </c>
       <c r="R11" t="n">
-        <v>7322002</v>
+        <v>7322053</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,43 +1765,27 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135326359</v>
+        <v>135323526</v>
       </c>
       <c r="B12" t="n">
         <v>92245</v>
@@ -1828,17 +1816,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619563</v>
+        <v>619613</v>
       </c>
       <c r="R12" t="n">
-        <v>7322050</v>
+        <v>7321994</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,23 +1880,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135330917</v>
+        <v>135323528</v>
       </c>
       <c r="B13" t="n">
         <v>92245</v>
@@ -1939,17 +1923,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619675</v>
+        <v>619630</v>
       </c>
       <c r="R13" t="n">
-        <v>7321985</v>
+        <v>7322002</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1988,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,30 +1983,46 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135325581</v>
+        <v>135326359</v>
       </c>
       <c r="B14" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,37 +2030,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619648</v>
+        <v>619563</v>
       </c>
       <c r="R14" t="n">
-        <v>7322061</v>
+        <v>7322050</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,12 +2114,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2130,45 +2130,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135325575</v>
+        <v>135330917</v>
       </c>
       <c r="B15" t="n">
-        <v>92795</v>
+        <v>92245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619645</v>
+        <v>619675</v>
       </c>
       <c r="R15" t="n">
-        <v>7322036</v>
+        <v>7321985</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2225,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2241,45 +2241,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135329802</v>
+        <v>135325581</v>
       </c>
       <c r="B16" t="n">
-        <v>92795</v>
+        <v>79452</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619620</v>
+        <v>619648</v>
       </c>
       <c r="R16" t="n">
-        <v>7321986</v>
+        <v>7322061</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2321,12 +2321,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Granlåga nedbruten</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,12 +2336,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2357,7 +2352,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135330939</v>
+        <v>135325575</v>
       </c>
       <c r="B17" t="n">
         <v>92795</v>
@@ -2388,17 +2383,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619595</v>
+        <v>619645</v>
       </c>
       <c r="R17" t="n">
-        <v>7322033</v>
+        <v>7322036</v>
       </c>
       <c r="S17" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2427,7 +2422,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2437,7 +2432,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,12 +2447,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2468,48 +2463,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135323123</v>
+        <v>135329802</v>
       </c>
       <c r="B18" t="n">
-        <v>91970</v>
+        <v>92795</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619600</v>
+        <v>619620</v>
       </c>
       <c r="R18" t="n">
-        <v>7322016</v>
+        <v>7321986</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2538,7 +2533,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2548,7 +2543,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Granlåga nedbruten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,12 +2563,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2579,48 +2579,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135329816</v>
+        <v>135330939</v>
       </c>
       <c r="B19" t="n">
-        <v>91970</v>
+        <v>92795</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619665</v>
+        <v>619595</v>
       </c>
       <c r="R19" t="n">
-        <v>7321974</v>
+        <v>7322033</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,12 +2674,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2690,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135323527</v>
+        <v>135323123</v>
       </c>
       <c r="B20" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,37 +2701,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619616</v>
+        <v>619600</v>
       </c>
       <c r="R20" t="n">
-        <v>7321993</v>
+        <v>7322016</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,22 +2785,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135325573</v>
+        <v>135329816</v>
       </c>
       <c r="B21" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,34 +2812,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619652</v>
+        <v>619665</v>
       </c>
       <c r="R21" t="n">
-        <v>7322003</v>
+        <v>7321974</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2867,7 +2871,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2877,7 +2881,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,12 +2896,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2908,7 +2912,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135326358</v>
+        <v>135323527</v>
       </c>
       <c r="B22" t="n">
         <v>91974</v>
@@ -2939,17 +2943,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619562</v>
+        <v>619616</v>
       </c>
       <c r="R22" t="n">
-        <v>7322050</v>
+        <v>7321993</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2978,7 +2982,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2988,7 +2992,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,23 +3007,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135326498</v>
+        <v>135325573</v>
       </c>
       <c r="B23" t="n">
         <v>91974</v>
@@ -3050,17 +3050,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619590</v>
+        <v>619652</v>
       </c>
       <c r="R23" t="n">
-        <v>7321974</v>
+        <v>7322003</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,12 +3114,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3130,7 +3130,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135330914</v>
+        <v>135326358</v>
       </c>
       <c r="B24" t="n">
         <v>91974</v>
@@ -3161,17 +3161,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619658</v>
+        <v>619562</v>
       </c>
       <c r="R24" t="n">
-        <v>7321989</v>
+        <v>7322050</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3225,12 +3225,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3241,7 +3241,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135330915</v>
+        <v>135326498</v>
       </c>
       <c r="B25" t="n">
         <v>91974</v>
@@ -3272,17 +3272,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619675</v>
+        <v>619590</v>
       </c>
       <c r="R25" t="n">
-        <v>7321985</v>
+        <v>7321974</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3336,12 +3336,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3352,7 +3352,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135330924</v>
+        <v>135330914</v>
       </c>
       <c r="B26" t="n">
         <v>91974</v>
@@ -3387,13 +3387,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619608</v>
+        <v>619658</v>
       </c>
       <c r="R26" t="n">
-        <v>7322117</v>
+        <v>7321989</v>
       </c>
       <c r="S26" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,45 +3463,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135321343</v>
+        <v>135330915</v>
       </c>
       <c r="B27" t="n">
-        <v>91988</v>
+        <v>91974</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619549</v>
+        <v>619675</v>
       </c>
       <c r="R27" t="n">
-        <v>7322014</v>
+        <v>7321985</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3558,12 +3558,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3574,48 +3574,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135329804</v>
+        <v>135330924</v>
       </c>
       <c r="B28" t="n">
-        <v>91988</v>
+        <v>91974</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619573</v>
+        <v>619608</v>
       </c>
       <c r="R28" t="n">
-        <v>7322042</v>
+        <v>7322117</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3654,12 +3654,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Låga</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3674,12 +3669,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3690,48 +3685,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135325577</v>
+        <v>135321343</v>
       </c>
       <c r="B29" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619649</v>
+        <v>619549</v>
       </c>
       <c r="R29" t="n">
-        <v>7322046</v>
+        <v>7322014</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3760,7 +3755,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3770,7 +3765,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3785,12 +3780,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3801,45 +3796,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135325579</v>
+        <v>135329804</v>
       </c>
       <c r="B30" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619647</v>
+        <v>619573</v>
       </c>
       <c r="R30" t="n">
-        <v>7322063</v>
+        <v>7322042</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3871,7 +3866,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3881,7 +3876,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3896,12 +3896,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3912,7 +3912,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135325586</v>
+        <v>135325577</v>
       </c>
       <c r="B31" t="n">
         <v>83222</v>
@@ -3947,13 +3947,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>619561</v>
+        <v>619649</v>
       </c>
       <c r="R31" t="n">
-        <v>7322179</v>
+        <v>7322046</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4023,7 +4023,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135326499</v>
+        <v>135325579</v>
       </c>
       <c r="B32" t="n">
         <v>83222</v>
@@ -4054,17 +4054,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>619565</v>
+        <v>619647</v>
       </c>
       <c r="R32" t="n">
-        <v>7322000</v>
+        <v>7322063</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4118,12 +4118,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4134,45 +4134,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135323535</v>
+        <v>135325586</v>
       </c>
       <c r="B33" t="n">
-        <v>92318</v>
+        <v>83222</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>619571</v>
+        <v>619561</v>
       </c>
       <c r="R33" t="n">
-        <v>7322010</v>
+        <v>7322179</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4225,46 +4225,30 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135323533</v>
+        <v>135326499</v>
       </c>
       <c r="B34" t="n">
-        <v>91896</v>
+        <v>83222</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4272,37 +4256,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3242</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619556</v>
+        <v>619565</v>
       </c>
       <c r="R34" t="n">
-        <v>7322012</v>
+        <v>7322000</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4331,7 +4315,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4341,7 +4325,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4352,81 +4336,65 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135322200</v>
+        <v>135323535</v>
       </c>
       <c r="B35" t="n">
-        <v>91937</v>
+        <v>92318</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>619552</v>
+        <v>619571</v>
       </c>
       <c r="R35" t="n">
-        <v>7322009</v>
+        <v>7322010</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4458,7 +4426,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4436,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4479,68 +4447,84 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135322204</v>
+        <v>135323533</v>
       </c>
       <c r="B36" t="n">
-        <v>91937</v>
+        <v>91896</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>619650</v>
+        <v>619556</v>
       </c>
       <c r="R36" t="n">
-        <v>7322160</v>
+        <v>7322012</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4569,7 +4553,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4563,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4590,27 +4574,43 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135323531</v>
+        <v>135322200</v>
       </c>
       <c r="B37" t="n">
         <v>91937</v>
@@ -4641,17 +4641,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>619624</v>
+        <v>619552</v>
       </c>
       <c r="R37" t="n">
-        <v>7322025</v>
+        <v>7322009</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4705,57 +4705,61 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135325580</v>
+        <v>135322204</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>619647</v>
+        <v>619650</v>
       </c>
       <c r="R38" t="n">
-        <v>7322062</v>
+        <v>7322160</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4787,7 +4791,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4797,7 +4801,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4812,12 +4816,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4828,48 +4832,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135325595</v>
+        <v>135323531</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>619537</v>
+        <v>619624</v>
       </c>
       <c r="R39" t="n">
-        <v>7322086</v>
+        <v>7322025</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4898,7 +4902,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4908,7 +4912,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,64 +4927,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135326505</v>
+        <v>135325580</v>
       </c>
       <c r="B40" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>619507</v>
+        <v>619647</v>
       </c>
       <c r="R40" t="n">
-        <v>7322024</v>
+        <v>7322062</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5034,12 +5034,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5050,45 +5050,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135321361</v>
+        <v>135325595</v>
       </c>
       <c r="B41" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619595</v>
+        <v>619537</v>
       </c>
       <c r="R41" t="n">
-        <v>7322144</v>
+        <v>7322086</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5145,12 +5145,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5161,48 +5161,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135321364</v>
+        <v>135326505</v>
       </c>
       <c r="B42" t="n">
-        <v>78776</v>
+        <v>79397</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>619580</v>
+        <v>619507</v>
       </c>
       <c r="R42" t="n">
-        <v>7322118</v>
+        <v>7322024</v>
       </c>
       <c r="S42" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5256,12 +5256,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5272,7 +5272,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135323135</v>
+        <v>135321361</v>
       </c>
       <c r="B43" t="n">
         <v>78776</v>
@@ -5303,14 +5303,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>619656</v>
+        <v>619595</v>
       </c>
       <c r="R43" t="n">
-        <v>7322137</v>
+        <v>7322144</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5367,12 +5367,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5383,7 +5383,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135323142</v>
+        <v>135321364</v>
       </c>
       <c r="B44" t="n">
         <v>78776</v>
@@ -5414,17 +5414,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>619605</v>
+        <v>619580</v>
       </c>
       <c r="R44" t="n">
-        <v>7322191</v>
+        <v>7322118</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5478,12 +5478,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5494,7 +5494,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135323144</v>
+        <v>135323135</v>
       </c>
       <c r="B45" t="n">
         <v>78776</v>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>619545</v>
+        <v>619656</v>
       </c>
       <c r="R45" t="n">
-        <v>7322155</v>
+        <v>7322137</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5605,7 +5605,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135325583</v>
+        <v>135323142</v>
       </c>
       <c r="B46" t="n">
         <v>78776</v>
@@ -5636,17 +5636,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>619639</v>
+        <v>619605</v>
       </c>
       <c r="R46" t="n">
-        <v>7322093</v>
+        <v>7322191</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5700,12 +5700,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5716,7 +5716,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135326502</v>
+        <v>135323144</v>
       </c>
       <c r="B47" t="n">
         <v>78776</v>
@@ -5751,13 +5751,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>619511</v>
+        <v>619545</v>
       </c>
       <c r="R47" t="n">
-        <v>7322024</v>
+        <v>7322155</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5811,12 +5811,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5827,7 +5827,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135329821</v>
+        <v>135325583</v>
       </c>
       <c r="B48" t="n">
         <v>78776</v>
@@ -5858,14 +5858,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>619634</v>
+        <v>619639</v>
       </c>
       <c r="R48" t="n">
-        <v>7321974</v>
+        <v>7322093</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5922,12 +5922,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5938,7 +5938,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135329832</v>
+        <v>135326502</v>
       </c>
       <c r="B49" t="n">
         <v>78776</v>
@@ -5969,14 +5969,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>619546</v>
+        <v>619511</v>
       </c>
       <c r="R49" t="n">
-        <v>7322084</v>
+        <v>7322024</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6033,12 +6033,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6049,7 +6049,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135330930</v>
+        <v>135329821</v>
       </c>
       <c r="B50" t="n">
         <v>78776</v>
@@ -6080,17 +6080,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619612</v>
+        <v>619634</v>
       </c>
       <c r="R50" t="n">
-        <v>7322185</v>
+        <v>7321974</v>
       </c>
       <c r="S50" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6144,12 +6144,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6160,10 +6160,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135323129</v>
+        <v>135329832</v>
       </c>
       <c r="B51" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6171,37 +6171,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>619604</v>
+        <v>619546</v>
       </c>
       <c r="R51" t="n">
-        <v>7322043</v>
+        <v>7322084</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6255,12 +6255,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6271,10 +6271,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135325571</v>
+        <v>135330930</v>
       </c>
       <c r="B52" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6282,37 +6282,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>619631</v>
+        <v>619612</v>
       </c>
       <c r="R52" t="n">
-        <v>7322000</v>
+        <v>7322185</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6366,12 +6366,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6382,7 +6382,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135325584</v>
+        <v>135323129</v>
       </c>
       <c r="B53" t="n">
         <v>83358</v>
@@ -6413,17 +6413,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>619575</v>
+        <v>619604</v>
       </c>
       <c r="R53" t="n">
-        <v>7322155</v>
+        <v>7322043</v>
       </c>
       <c r="S53" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6477,12 +6477,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6493,7 +6493,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135325589</v>
+        <v>135325571</v>
       </c>
       <c r="B54" t="n">
         <v>83358</v>
@@ -6528,10 +6528,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>619490</v>
+        <v>619631</v>
       </c>
       <c r="R54" t="n">
-        <v>7322171</v>
+        <v>7322000</v>
       </c>
       <c r="S54" t="n">
         <v>6</v>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6604,10 +6604,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135321549</v>
+        <v>135325584</v>
       </c>
       <c r="B55" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>619576</v>
+        <v>619575</v>
       </c>
       <c r="R55" t="n">
-        <v>7322127</v>
+        <v>7322155</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6699,12 +6699,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6715,10 +6715,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135322202</v>
+        <v>135325589</v>
       </c>
       <c r="B56" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6726,37 +6726,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>619550</v>
+        <v>619490</v>
       </c>
       <c r="R56" t="n">
-        <v>7322004</v>
+        <v>7322171</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6810,12 +6810,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6826,7 +6826,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135322205</v>
+        <v>135321549</v>
       </c>
       <c r="B57" t="n">
         <v>79992</v>
@@ -6857,17 +6857,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>619648</v>
+        <v>619576</v>
       </c>
       <c r="R57" t="n">
-        <v>7322202</v>
+        <v>7322127</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6921,12 +6921,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6937,7 +6937,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135323132</v>
+        <v>135322202</v>
       </c>
       <c r="B58" t="n">
         <v>79992</v>
@@ -6968,17 +6968,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>619609</v>
+        <v>619550</v>
       </c>
       <c r="R58" t="n">
-        <v>7322073</v>
+        <v>7322004</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7032,12 +7032,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7048,7 +7048,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135323145</v>
+        <v>135322205</v>
       </c>
       <c r="B59" t="n">
         <v>79992</v>
@@ -7079,17 +7079,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>619557</v>
+        <v>619648</v>
       </c>
       <c r="R59" t="n">
-        <v>7322144</v>
+        <v>7322202</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7143,12 +7143,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7159,7 +7159,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135325572</v>
+        <v>135323132</v>
       </c>
       <c r="B60" t="n">
         <v>79992</v>
@@ -7190,17 +7190,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>619648</v>
+        <v>619609</v>
       </c>
       <c r="R60" t="n">
-        <v>7321997</v>
+        <v>7322073</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7254,12 +7254,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7270,7 +7270,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135325594</v>
+        <v>135323145</v>
       </c>
       <c r="B61" t="n">
         <v>79992</v>
@@ -7301,17 +7301,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>619516</v>
+        <v>619557</v>
       </c>
       <c r="R61" t="n">
-        <v>7322084</v>
+        <v>7322144</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7365,12 +7365,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7381,7 +7381,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135326504</v>
+        <v>135325572</v>
       </c>
       <c r="B62" t="n">
         <v>79992</v>
@@ -7412,17 +7412,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>619507</v>
+        <v>619648</v>
       </c>
       <c r="R62" t="n">
-        <v>7322024</v>
+        <v>7321997</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7476,12 +7476,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7492,7 +7492,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135329819</v>
+        <v>135325594</v>
       </c>
       <c r="B63" t="n">
         <v>79992</v>
@@ -7523,17 +7523,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>619650</v>
+        <v>619516</v>
       </c>
       <c r="R63" t="n">
-        <v>7321988</v>
+        <v>7322084</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7587,12 +7587,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7603,7 +7603,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135329831</v>
+        <v>135326504</v>
       </c>
       <c r="B64" t="n">
         <v>79992</v>
@@ -7634,14 +7634,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>619545</v>
+        <v>619507</v>
       </c>
       <c r="R64" t="n">
-        <v>7322092</v>
+        <v>7322024</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7698,12 +7698,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7714,45 +7714,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135325590</v>
+        <v>135329819</v>
       </c>
       <c r="B65" t="n">
-        <v>80500</v>
+        <v>79992</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>619458</v>
+        <v>619650</v>
       </c>
       <c r="R65" t="n">
-        <v>7322119</v>
+        <v>7321988</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7809,12 +7809,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7825,10 +7825,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135321366</v>
+        <v>135329831</v>
       </c>
       <c r="B66" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7836,21 +7836,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7860,13 +7860,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>619580</v>
+        <v>619545</v>
       </c>
       <c r="R66" t="n">
-        <v>7322117</v>
+        <v>7322092</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7920,12 +7920,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7936,48 +7936,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135323134</v>
+        <v>135325590</v>
       </c>
       <c r="B67" t="n">
-        <v>78377</v>
+        <v>80500</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619656</v>
+        <v>619458</v>
       </c>
       <c r="R67" t="n">
-        <v>7322136</v>
+        <v>7322119</v>
       </c>
       <c r="S67" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8031,12 +8031,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8047,7 +8047,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135323141</v>
+        <v>135321366</v>
       </c>
       <c r="B68" t="n">
         <v>78377</v>
@@ -8078,17 +8078,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>619605</v>
+        <v>619580</v>
       </c>
       <c r="R68" t="n">
-        <v>7322191</v>
+        <v>7322117</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8142,12 +8142,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8158,7 +8158,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135325582</v>
+        <v>135323134</v>
       </c>
       <c r="B69" t="n">
         <v>78377</v>
@@ -8189,17 +8189,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>619634</v>
+        <v>619656</v>
       </c>
       <c r="R69" t="n">
-        <v>7322092</v>
+        <v>7322136</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8253,12 +8253,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8269,7 +8269,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135326506</v>
+        <v>135323141</v>
       </c>
       <c r="B70" t="n">
         <v>78377</v>
@@ -8304,13 +8304,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>619505</v>
+        <v>619605</v>
       </c>
       <c r="R70" t="n">
-        <v>7322017</v>
+        <v>7322191</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8364,12 +8364,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8380,10 +8380,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135321369</v>
+        <v>135325582</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8391,45 +8391,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619598</v>
+        <v>619634</v>
       </c>
       <c r="R71" t="n">
-        <v>7322108</v>
+        <v>7322092</v>
       </c>
       <c r="S71" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8458,7 +8450,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8468,12 +8460,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8488,12 +8475,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8504,10 +8491,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135321371</v>
+        <v>135326506</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8515,45 +8502,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>619575</v>
+        <v>619505</v>
       </c>
       <c r="R72" t="n">
-        <v>7322044</v>
+        <v>7322017</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8582,7 +8561,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8592,12 +8571,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8612,12 +8586,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8628,7 +8602,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135323143</v>
+        <v>135321369</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8657,24 +8631,27 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619588</v>
+        <v>619598</v>
       </c>
       <c r="R73" t="n">
-        <v>7322173</v>
+        <v>7322108</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8703,7 +8680,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8713,7 +8690,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8728,12 +8710,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8744,7 +8726,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135323524</v>
+        <v>135321371</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8773,16 +8755,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>619644</v>
+        <v>619575</v>
       </c>
       <c r="R74" t="n">
-        <v>7321971</v>
+        <v>7322044</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8814,7 +8804,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8824,12 +8814,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8844,19 +8834,23 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135326508</v>
+        <v>135323143</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8887,7 +8881,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8896,13 +8890,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>619441</v>
+        <v>619588</v>
       </c>
       <c r="R75" t="n">
-        <v>7322009</v>
+        <v>7322173</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8931,7 +8925,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8941,12 +8935,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8961,12 +8950,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8977,7 +8966,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135326509</v>
+        <v>135323524</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -9006,24 +8995,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>619463</v>
+        <v>619644</v>
       </c>
       <c r="R76" t="n">
-        <v>7321984</v>
+        <v>7321971</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9052,7 +9036,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9062,12 +9046,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9082,23 +9066,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135326510</v>
+        <v>135326508</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -9129,7 +9109,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9138,10 +9118,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>619498</v>
+        <v>619441</v>
       </c>
       <c r="R77" t="n">
-        <v>7321987</v>
+        <v>7322009</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9173,7 +9153,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9183,12 +9163,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9219,7 +9199,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135329836</v>
+        <v>135326509</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9248,16 +9228,21 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>619599</v>
+        <v>619463</v>
       </c>
       <c r="R78" t="n">
-        <v>7321991</v>
+        <v>7321984</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9289,7 +9274,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9299,12 +9284,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9319,12 +9304,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9335,7 +9320,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135330913</v>
+        <v>135326510</v>
       </c>
       <c r="B79" t="n">
         <v>57975</v>
@@ -9364,27 +9349,24 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>619674</v>
+        <v>619498</v>
       </c>
       <c r="R79" t="n">
-        <v>7321952</v>
+        <v>7321987</v>
       </c>
       <c r="S79" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9413,7 +9395,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9423,12 +9405,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9443,12 +9425,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9459,7 +9441,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135330918</v>
+        <v>135329836</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -9488,27 +9470,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619657</v>
+        <v>619599</v>
       </c>
       <c r="R80" t="n">
-        <v>7322019</v>
+        <v>7321991</v>
       </c>
       <c r="S80" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9537,7 +9511,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9547,12 +9521,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9567,12 +9541,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9583,7 +9557,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135330920</v>
+        <v>135330913</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -9626,13 +9600,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619636</v>
+        <v>619674</v>
       </c>
       <c r="R81" t="n">
-        <v>7322057</v>
+        <v>7321952</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9661,7 +9635,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9671,12 +9645,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Spår från födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9707,7 +9681,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135330921</v>
+        <v>135330918</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -9740,7 +9714,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -9750,13 +9724,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619615</v>
+        <v>619657</v>
       </c>
       <c r="R82" t="n">
-        <v>7322104</v>
+        <v>7322019</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9785,7 +9759,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9795,12 +9769,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9831,7 +9805,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135330922</v>
+        <v>135330920</v>
       </c>
       <c r="B83" t="n">
         <v>57975</v>
@@ -9864,7 +9838,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -9874,13 +9848,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>619616</v>
+        <v>619636</v>
       </c>
       <c r="R83" t="n">
-        <v>7322103</v>
+        <v>7322057</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9909,7 +9883,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9919,12 +9893,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår från födosök</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9955,7 +9929,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135330925</v>
+        <v>135330921</v>
       </c>
       <c r="B84" t="n">
         <v>57975</v>
@@ -9988,7 +9962,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -9998,13 +9972,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>619617</v>
+        <v>619615</v>
       </c>
       <c r="R84" t="n">
-        <v>7322138</v>
+        <v>7322104</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10033,7 +10007,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10043,12 +10017,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10079,7 +10053,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135330926</v>
+        <v>135330922</v>
       </c>
       <c r="B85" t="n">
         <v>57975</v>
@@ -10112,7 +10086,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -10122,13 +10096,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>619652</v>
+        <v>619616</v>
       </c>
       <c r="R85" t="n">
-        <v>7322160</v>
+        <v>7322103</v>
       </c>
       <c r="S85" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10157,7 +10131,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10167,12 +10141,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10203,7 +10177,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135330929</v>
+        <v>135330925</v>
       </c>
       <c r="B86" t="n">
         <v>57975</v>
@@ -10236,7 +10210,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10246,13 +10220,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>619619</v>
+        <v>619617</v>
       </c>
       <c r="R86" t="n">
-        <v>7322169</v>
+        <v>7322138</v>
       </c>
       <c r="S86" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10281,7 +10255,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10291,12 +10265,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10327,7 +10301,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135330931</v>
+        <v>135330926</v>
       </c>
       <c r="B87" t="n">
         <v>57975</v>
@@ -10360,7 +10334,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -10370,13 +10344,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>619590</v>
+        <v>619652</v>
       </c>
       <c r="R87" t="n">
-        <v>7322174</v>
+        <v>7322160</v>
       </c>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10405,7 +10379,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10415,12 +10389,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10451,7 +10425,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135330935</v>
+        <v>135330929</v>
       </c>
       <c r="B88" t="n">
         <v>57975</v>
@@ -10484,7 +10458,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -10494,13 +10468,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>619577</v>
+        <v>619619</v>
       </c>
       <c r="R88" t="n">
-        <v>7322144</v>
+        <v>7322169</v>
       </c>
       <c r="S88" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10529,7 +10503,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10539,12 +10513,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10575,7 +10549,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135330936</v>
+        <v>135330931</v>
       </c>
       <c r="B89" t="n">
         <v>57975</v>
@@ -10618,13 +10592,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>619598</v>
+        <v>619590</v>
       </c>
       <c r="R89" t="n">
-        <v>7322107</v>
+        <v>7322174</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10653,7 +10627,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10663,7 +10637,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10699,7 +10673,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135330938</v>
+        <v>135330935</v>
       </c>
       <c r="B90" t="n">
         <v>57975</v>
@@ -10742,13 +10716,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>619571</v>
+        <v>619577</v>
       </c>
       <c r="R90" t="n">
-        <v>7322045</v>
+        <v>7322144</v>
       </c>
       <c r="S90" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10777,7 +10751,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10787,7 +10761,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10823,48 +10797,56 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135325591</v>
+        <v>135330936</v>
       </c>
       <c r="B91" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>619449</v>
+        <v>619598</v>
       </c>
       <c r="R91" t="n">
-        <v>7322120</v>
+        <v>7322107</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10893,7 +10875,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10903,7 +10885,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10918,12 +10905,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10934,10 +10921,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135323146</v>
+        <v>135330938</v>
       </c>
       <c r="B92" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10945,37 +10932,45 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>619591</v>
+        <v>619571</v>
       </c>
       <c r="R92" t="n">
-        <v>7322093</v>
+        <v>7322045</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11004,7 +10999,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11014,7 +11009,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11029,12 +11029,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11045,48 +11045,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135323532</v>
+        <v>135325591</v>
       </c>
       <c r="B93" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>619540</v>
+        <v>619449</v>
       </c>
       <c r="R93" t="n">
-        <v>7322034</v>
+        <v>7322120</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11140,19 +11140,23 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135325587</v>
+        <v>135323146</v>
       </c>
       <c r="B94" t="n">
         <v>58136</v>
@@ -11183,17 +11187,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>619517</v>
+        <v>619591</v>
       </c>
       <c r="R94" t="n">
-        <v>7322182</v>
+        <v>7322093</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11222,7 +11226,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11232,7 +11236,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11247,12 +11251,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11263,7 +11267,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135326500</v>
+        <v>135323532</v>
       </c>
       <c r="B95" t="n">
         <v>58136</v>
@@ -11291,29 +11295,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>619528</v>
+        <v>619540</v>
       </c>
       <c r="R95" t="n">
-        <v>7322006</v>
+        <v>7322034</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11342,7 +11337,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11352,7 +11347,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11367,23 +11362,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135330933</v>
+        <v>135325587</v>
       </c>
       <c r="B96" t="n">
         <v>58136</v>
@@ -11412,27 +11403,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>619580</v>
+        <v>619517</v>
       </c>
       <c r="R96" t="n">
-        <v>7322161</v>
+        <v>7322182</v>
       </c>
       <c r="S96" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11486,12 +11469,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11502,7 +11485,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135330937</v>
+        <v>135326500</v>
       </c>
       <c r="B97" t="n">
         <v>58136</v>
@@ -11530,28 +11513,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>619572</v>
+        <v>619528</v>
       </c>
       <c r="R97" t="n">
-        <v>7322048</v>
+        <v>7322006</v>
       </c>
       <c r="S97" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11580,7 +11564,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11590,7 +11574,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11605,12 +11589,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11621,10 +11605,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135321349</v>
+        <v>135330933</v>
       </c>
       <c r="B98" t="n">
-        <v>78382</v>
+        <v>58136</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11632,37 +11616,45 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>619627</v>
+        <v>619580</v>
       </c>
       <c r="R98" t="n">
-        <v>7322118</v>
+        <v>7322161</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11691,7 +11683,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11701,7 +11693,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11716,12 +11708,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11732,10 +11724,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135323128</v>
+        <v>135330937</v>
       </c>
       <c r="B99" t="n">
-        <v>78382</v>
+        <v>58136</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11743,37 +11735,45 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>619549</v>
+        <v>619572</v>
       </c>
       <c r="R99" t="n">
-        <v>7322008</v>
+        <v>7322048</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11827,12 +11827,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11843,10 +11843,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135323131</v>
+        <v>135336188</v>
       </c>
       <c r="B100" t="n">
-        <v>78382</v>
+        <v>41606</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11854,37 +11854,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>215713</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>619607</v>
+        <v>619649</v>
       </c>
       <c r="R100" t="n">
-        <v>7322071</v>
+        <v>7322021</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11913,7 +11918,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11923,7 +11928,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11938,12 +11943,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11954,7 +11959,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135323133</v>
+        <v>135321349</v>
       </c>
       <c r="B101" t="n">
         <v>78382</v>
@@ -11985,17 +11990,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>619624</v>
+        <v>619627</v>
       </c>
       <c r="R101" t="n">
-        <v>7322126</v>
+        <v>7322118</v>
       </c>
       <c r="S101" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12049,12 +12054,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12065,7 +12070,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135326507</v>
+        <v>135323128</v>
       </c>
       <c r="B102" t="n">
         <v>78382</v>
@@ -12100,13 +12105,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>619502</v>
+        <v>619549</v>
       </c>
       <c r="R102" t="n">
-        <v>7322009</v>
+        <v>7322008</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12135,7 +12140,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12145,7 +12150,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12160,12 +12165,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12176,10 +12181,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135326503</v>
+        <v>135323131</v>
       </c>
       <c r="B103" t="n">
-        <v>79963</v>
+        <v>78382</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12187,21 +12192,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>228579</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12211,13 +12216,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>619511</v>
+        <v>619607</v>
       </c>
       <c r="R103" t="n">
-        <v>7322024</v>
+        <v>7322071</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12246,7 +12251,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12256,7 +12261,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12271,12 +12276,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12287,10 +12292,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135321359</v>
+        <v>135323133</v>
       </c>
       <c r="B104" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12298,37 +12303,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>619585</v>
+        <v>619624</v>
       </c>
       <c r="R104" t="n">
-        <v>7322120</v>
+        <v>7322126</v>
       </c>
       <c r="S104" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12357,7 +12362,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12367,7 +12372,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12382,12 +12387,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12398,10 +12403,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135323530</v>
+        <v>135326507</v>
       </c>
       <c r="B105" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12409,37 +12414,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>619609</v>
+        <v>619502</v>
       </c>
       <c r="R105" t="n">
-        <v>7322000</v>
+        <v>7322009</v>
       </c>
       <c r="S105" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12468,7 +12473,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12478,7 +12483,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12493,22 +12498,26 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135329830</v>
+        <v>135326503</v>
       </c>
       <c r="B106" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12516,34 +12525,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>619599</v>
+        <v>619511</v>
       </c>
       <c r="R106" t="n">
-        <v>7322098</v>
+        <v>7322024</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12575,7 +12584,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12585,7 +12594,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12600,12 +12609,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12616,10 +12625,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135323529</v>
+        <v>135321359</v>
       </c>
       <c r="B107" t="n">
-        <v>92366</v>
+        <v>79396</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12627,37 +12636,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6040186</v>
+        <v>260591</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>619629</v>
+        <v>619585</v>
       </c>
       <c r="R107" t="n">
-        <v>7321999</v>
+        <v>7322120</v>
       </c>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12686,7 +12695,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12696,7 +12705,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12705,42 +12714,371 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>135323530</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>619609</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7322000</v>
+      </c>
+      <c r="S108" t="n">
+        <v>7</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
+      <c r="AX108" t="inlineStr">
         <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AY107" t="inlineStr"/>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>135329830</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Maskaure Uddnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>619599</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7322098</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>135323529</v>
+      </c>
+      <c r="B110" t="n">
+        <v>92366</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>619629</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7321999</v>
+      </c>
+      <c r="S110" t="n">
+        <v>7</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka, Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AZ110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323935</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325593</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323934</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325592</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323126</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323140</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321345</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322203</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323127</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323130</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323526</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323528</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2127,6 +2192,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326359</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2238,6 +2308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330917</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2349,6 +2424,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325581</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2460,6 +2540,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325575</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329802</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2687,6 +2777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330939</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2798,6 +2893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323123</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2909,6 +3009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329816</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3016,6 +3121,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323527</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3127,6 +3237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325573</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3238,6 +3353,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326358</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3349,6 +3469,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326498</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3460,6 +3585,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330914</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3571,6 +3701,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330915</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3682,6 +3817,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330924</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3793,6 +3933,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321343</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3909,6 +4054,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329804</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4020,6 +4170,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325577</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4131,6 +4286,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325579</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4242,6 +4402,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325586</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4353,6 +4518,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326499</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4480,6 +4650,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323535</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4607,6 +4782,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323533</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4718,6 +4898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322200</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4829,6 +5014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322204</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4936,6 +5126,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323531</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5047,6 +5242,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325580</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5158,6 +5358,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325595</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5269,6 +5474,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326505</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5380,6 +5590,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321361</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5491,6 +5706,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321364</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5602,6 +5822,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323135</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5713,6 +5938,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323142</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5824,6 +6054,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323144</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5935,6 +6170,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325583</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6046,6 +6286,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326502</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6157,6 +6402,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329821</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6268,6 +6518,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329832</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6379,6 +6634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330930</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6490,6 +6750,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323129</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6601,6 +6866,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325571</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6712,6 +6982,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325584</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6823,6 +7098,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325589</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6934,6 +7214,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321549</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7045,6 +7330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322202</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7156,6 +7446,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322205</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7267,6 +7562,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323132</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7378,6 +7678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323145</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7489,6 +7794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325572</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7600,6 +7910,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325594</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7711,6 +8026,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326504</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7822,6 +8142,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329819</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7933,6 +8258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329831</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8044,6 +8374,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325590</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8155,6 +8490,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321366</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8266,6 +8606,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323134</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8377,6 +8722,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323141</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8488,6 +8838,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325582</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8599,6 +8954,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326506</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8723,6 +9083,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321369</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8847,6 +9212,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321371</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8963,6 +9333,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323143</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9075,6 +9450,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323524</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9196,6 +9576,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326508</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9317,6 +9702,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326509</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9438,6 +9828,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326510</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9554,6 +9949,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329836</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9678,6 +10078,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330913</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9802,6 +10207,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330918</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9926,6 +10336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330920</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10050,6 +10465,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330921</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10174,6 +10594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330922</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10298,6 +10723,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330925</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10422,6 +10852,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330926</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10546,6 +10981,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330929</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10670,6 +11110,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330931</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10794,6 +11239,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330935</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10918,6 +11368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330936</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11042,6 +11497,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330938</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11153,6 +11613,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325591</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11264,6 +11729,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323146</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11371,6 +11841,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323532</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11482,6 +11957,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325587</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11602,6 +12082,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326500</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11721,6 +12206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330933</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11840,6 +12330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330937</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11956,6 +12451,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336188</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12067,6 +12567,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321349</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12178,6 +12683,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323128</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12289,6 +12799,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323131</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12400,6 +12915,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323133</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12511,6 +13031,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326507</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12622,6 +13147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326503</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12733,6 +13263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321359</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12840,6 +13375,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323530</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12951,6 +13491,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329830</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13079,8 +13624,124 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323529</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323935</v>
       </c>
       <c r="B2" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135325593</v>
       </c>
       <c r="B3" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135323934</v>
       </c>
       <c r="B4" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135325592</v>
       </c>
       <c r="B5" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135323126</v>
       </c>
       <c r="B6" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135323140</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135321345</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135322203</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135323127</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135323130</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135323526</v>
       </c>
       <c r="B12" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135323528</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135326359</v>
       </c>
       <c r="B14" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>135330917</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135325581</v>
       </c>
       <c r="B16" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>135325575</v>
       </c>
       <c r="B17" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>135329802</v>
       </c>
       <c r="B18" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>135330939</v>
       </c>
       <c r="B19" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>135323123</v>
       </c>
       <c r="B20" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>135329816</v>
       </c>
       <c r="B21" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135323527</v>
       </c>
       <c r="B22" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135325573</v>
       </c>
       <c r="B23" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135326358</v>
       </c>
       <c r="B24" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135326498</v>
       </c>
       <c r="B25" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135330914</v>
       </c>
       <c r="B26" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135330915</v>
       </c>
       <c r="B27" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135330924</v>
       </c>
       <c r="B28" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>135321343</v>
       </c>
       <c r="B29" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>135329804</v>
       </c>
       <c r="B30" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>135325577</v>
       </c>
       <c r="B31" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>135325579</v>
       </c>
       <c r="B32" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135325586</v>
       </c>
       <c r="B33" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>135326499</v>
       </c>
       <c r="B34" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>135323535</v>
       </c>
       <c r="B35" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>135323533</v>
       </c>
       <c r="B36" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>135322200</v>
       </c>
       <c r="B37" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135322204</v>
       </c>
       <c r="B38" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>135323531</v>
       </c>
       <c r="B39" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>135325580</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>135325595</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>135326505</v>
       </c>
       <c r="B42" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>135321361</v>
       </c>
       <c r="B43" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135321364</v>
       </c>
       <c r="B44" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>135323135</v>
       </c>
       <c r="B45" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>135323142</v>
       </c>
       <c r="B46" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135323144</v>
       </c>
       <c r="B47" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>135325583</v>
       </c>
       <c r="B48" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>135326502</v>
       </c>
       <c r="B49" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>135329821</v>
       </c>
       <c r="B50" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>135329832</v>
       </c>
       <c r="B51" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135330930</v>
       </c>
       <c r="B52" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>135323129</v>
       </c>
       <c r="B53" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>135325571</v>
       </c>
       <c r="B54" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>135325584</v>
       </c>
       <c r="B55" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>135325589</v>
       </c>
       <c r="B56" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>135321549</v>
       </c>
       <c r="B57" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>135322202</v>
       </c>
       <c r="B58" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>135322205</v>
       </c>
       <c r="B59" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>135323132</v>
       </c>
       <c r="B60" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135323145</v>
       </c>
       <c r="B61" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>135325572</v>
       </c>
       <c r="B62" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135325594</v>
       </c>
       <c r="B63" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>135326504</v>
       </c>
       <c r="B64" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>135329819</v>
       </c>
       <c r="B65" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>135329831</v>
       </c>
       <c r="B66" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>135325590</v>
       </c>
       <c r="B67" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135321366</v>
       </c>
       <c r="B68" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>135323134</v>
       </c>
       <c r="B69" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>135323141</v>
       </c>
       <c r="B70" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135325582</v>
       </c>
       <c r="B71" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>135326506</v>
       </c>
       <c r="B72" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>135321369</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>135321371</v>
       </c>
       <c r="B74" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>135323143</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>135323524</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>135326508</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>135326509</v>
       </c>
       <c r="B78" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>135326510</v>
       </c>
       <c r="B79" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>135329836</v>
       </c>
       <c r="B80" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>135330913</v>
       </c>
       <c r="B81" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>135330918</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>135330920</v>
       </c>
       <c r="B83" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>135330921</v>
       </c>
       <c r="B84" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>135330922</v>
       </c>
       <c r="B85" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>135330925</v>
       </c>
       <c r="B86" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>135330926</v>
       </c>
       <c r="B87" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>135330929</v>
       </c>
       <c r="B88" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>135330931</v>
       </c>
       <c r="B89" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>135330935</v>
       </c>
       <c r="B90" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>135330936</v>
       </c>
       <c r="B91" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>135330938</v>
       </c>
       <c r="B92" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>135325591</v>
       </c>
       <c r="B93" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>135323146</v>
       </c>
       <c r="B94" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>135323532</v>
       </c>
       <c r="B95" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>135325587</v>
       </c>
       <c r="B96" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>135326500</v>
       </c>
       <c r="B97" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>135330933</v>
       </c>
       <c r="B98" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>135330937</v>
       </c>
       <c r="B99" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>135336188</v>
       </c>
       <c r="B100" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>135321349</v>
       </c>
       <c r="B101" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>135323128</v>
       </c>
       <c r="B102" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>135323131</v>
       </c>
       <c r="B103" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>135323133</v>
       </c>
       <c r="B104" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>135326507</v>
       </c>
       <c r="B105" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>135326503</v>
       </c>
       <c r="B106" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>135321359</v>
       </c>
       <c r="B107" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>135323530</v>
       </c>
       <c r="B108" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>135329830</v>
       </c>
       <c r="B109" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>135323529</v>
       </c>
       <c r="B110" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323935</v>
       </c>
       <c r="B2" t="n">
-        <v>96722</v>
+        <v>96749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135325593</v>
       </c>
       <c r="B3" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135323934</v>
       </c>
       <c r="B4" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135325592</v>
       </c>
       <c r="B5" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135323126</v>
       </c>
       <c r="B6" t="n">
-        <v>92635</v>
+        <v>92662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135323140</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135321345</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135322203</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135323127</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135323130</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135323526</v>
       </c>
       <c r="B12" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135323528</v>
       </c>
       <c r="B13" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135326359</v>
       </c>
       <c r="B14" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>135330917</v>
       </c>
       <c r="B15" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135325581</v>
       </c>
       <c r="B16" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>135325575</v>
       </c>
       <c r="B17" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>135329802</v>
       </c>
       <c r="B18" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>135330939</v>
       </c>
       <c r="B19" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>135323123</v>
       </c>
       <c r="B20" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>135329816</v>
       </c>
       <c r="B21" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135323527</v>
       </c>
       <c r="B22" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135325573</v>
       </c>
       <c r="B23" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135326358</v>
       </c>
       <c r="B24" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135326498</v>
       </c>
       <c r="B25" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135330914</v>
       </c>
       <c r="B26" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135330915</v>
       </c>
       <c r="B27" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135330924</v>
       </c>
       <c r="B28" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>135321343</v>
       </c>
       <c r="B29" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>135329804</v>
       </c>
       <c r="B30" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>135325577</v>
       </c>
       <c r="B31" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>135325579</v>
       </c>
       <c r="B32" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135325586</v>
       </c>
       <c r="B33" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>135326499</v>
       </c>
       <c r="B34" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>135323535</v>
       </c>
       <c r="B35" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>135323533</v>
       </c>
       <c r="B36" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>135322200</v>
       </c>
       <c r="B37" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135322204</v>
       </c>
       <c r="B38" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>135323531</v>
       </c>
       <c r="B39" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>135325580</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>135325595</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>135326505</v>
       </c>
       <c r="B42" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>135321361</v>
       </c>
       <c r="B43" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135321364</v>
       </c>
       <c r="B44" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>135323135</v>
       </c>
       <c r="B45" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>135323142</v>
       </c>
       <c r="B46" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135323144</v>
       </c>
       <c r="B47" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>135325583</v>
       </c>
       <c r="B48" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>135326502</v>
       </c>
       <c r="B49" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>135329821</v>
       </c>
       <c r="B50" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>135329832</v>
       </c>
       <c r="B51" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135330930</v>
       </c>
       <c r="B52" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>135323129</v>
       </c>
       <c r="B53" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>135325571</v>
       </c>
       <c r="B54" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>135325584</v>
       </c>
       <c r="B55" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>135325589</v>
       </c>
       <c r="B56" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>135321549</v>
       </c>
       <c r="B57" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>135322202</v>
       </c>
       <c r="B58" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>135322205</v>
       </c>
       <c r="B59" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>135323132</v>
       </c>
       <c r="B60" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135323145</v>
       </c>
       <c r="B61" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>135325572</v>
       </c>
       <c r="B62" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135325594</v>
       </c>
       <c r="B63" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>135326504</v>
       </c>
       <c r="B64" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>135329819</v>
       </c>
       <c r="B65" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>135329831</v>
       </c>
       <c r="B66" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>135325590</v>
       </c>
       <c r="B67" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135321366</v>
       </c>
       <c r="B68" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>135323134</v>
       </c>
       <c r="B69" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>135323141</v>
       </c>
       <c r="B70" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135325582</v>
       </c>
       <c r="B71" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>135326506</v>
       </c>
       <c r="B72" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12462,7 +12462,7 @@
         <v>135321349</v>
       </c>
       <c r="B101" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>135323128</v>
       </c>
       <c r="B102" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>135323131</v>
       </c>
       <c r="B103" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>135323133</v>
       </c>
       <c r="B104" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>135326507</v>
       </c>
       <c r="B105" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>135326503</v>
       </c>
       <c r="B106" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>135321359</v>
       </c>
       <c r="B107" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>135323530</v>
       </c>
       <c r="B108" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>135329830</v>
       </c>
       <c r="B109" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>135323529</v>
       </c>
       <c r="B110" t="n">
-        <v>92408</v>
+        <v>92435</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323935</v>
       </c>
       <c r="B2" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135323934</v>
       </c>
       <c r="B4" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135323126</v>
       </c>
       <c r="B6" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135321345</v>
       </c>
       <c r="B8" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135322203</v>
       </c>
       <c r="B9" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135323127</v>
       </c>
       <c r="B10" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135323130</v>
       </c>
       <c r="B11" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135323526</v>
       </c>
       <c r="B12" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135323528</v>
       </c>
       <c r="B13" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135326359</v>
       </c>
       <c r="B14" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>135330917</v>
       </c>
       <c r="B15" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>135325575</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>135329802</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>135330939</v>
       </c>
       <c r="B19" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>135323123</v>
       </c>
       <c r="B20" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>135329816</v>
       </c>
       <c r="B21" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135323527</v>
       </c>
       <c r="B22" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135325573</v>
       </c>
       <c r="B23" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135326358</v>
       </c>
       <c r="B24" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135326498</v>
       </c>
       <c r="B25" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135330914</v>
       </c>
       <c r="B26" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135330915</v>
       </c>
       <c r="B27" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135330924</v>
       </c>
       <c r="B28" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>135321343</v>
       </c>
       <c r="B29" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>135329804</v>
       </c>
       <c r="B30" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>135323535</v>
       </c>
       <c r="B35" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>135323533</v>
       </c>
       <c r="B36" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>135322200</v>
       </c>
       <c r="B37" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135322204</v>
       </c>
       <c r="B38" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>135323531</v>
       </c>
       <c r="B39" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>135323529</v>
       </c>
       <c r="B110" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
+++ b/artfynd/Maskaure Uddnäs avvanm, 4,6 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323935</v>
       </c>
       <c r="B2" t="n">
-        <v>96756</v>
+        <v>96773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135323934</v>
       </c>
       <c r="B4" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>135336188</v>
       </c>
       <c r="B100" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
